--- a/l1/L1数据记录.xlsx
+++ b/l1/L1数据记录.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X28"/>
+  <dimension ref="A1:X30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1332,7 +1332,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>L1-24</t>
+          <t>L1-22</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1362,18 +1362,18 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>.dta×1</t>
+          <t>.dta×11</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>单段</t>
+          <t>同一采集、DAQ 按卷续写（11 卷，内容不重复）</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1409,21 +1409,21 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>7.37 J</t>
+          <t>25 mm(预置脱粘)</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>-4/-40 → -4.5/-45 → -5/-50 → -5.5/-55 → -6/-60</t>
+          <t>-3.5/-35 → -3.9/-39 → -4.5/-45 → -5/-50 → -5.5/-55 → -6/-60</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>20,000 + 75,000 + 25,000 + 62,000 + 60,000</t>
+          <t>10,000 + 10,000 + 10,000 + 170,000 + 85,000 + 60,000</t>
         </is>
       </c>
       <c r="U9" t="n">
-        <v>242000</v>
+        <v>345000</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>蒙皮侧: 冲击中心 115.0, 165; 传感器编号 反向（L5R1…L1R5）</t>
+          <t>蒙皮侧: 脱粘下缘(Y) 45</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -1444,27 +1444,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>L1-25</t>
+          <t>L1-23</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>既有</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>L1 谱载+FBG</t>
+          <t>L1 恒幅+FBG+DFOS</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>有</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1474,18 +1474,18 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>.dta×2</t>
+          <t>.pridb×1</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>分次加载（2 段，最长间隔 34 天）</t>
+          <t>单段</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1497,66 +1497,66 @@
         <v>10</v>
       </c>
       <c r="M10" t="n">
-        <v>3071</v>
+        <v>5</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>每 7 分钟 20 秒快照（全天覆盖，占空约 5%）</t>
+          <t>连续长记录</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>+8</t>
+          <t>+0</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
           <t>无</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>10 J</t>
+          <t>无冲击（PDF 标为脱粘）</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>-50.4/-75 → -50.4/-78</t>
+          <t>-5/-50 → -6/-60</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1,000,000 + 580,000</t>
+          <t>多级（见组内 PDF 的 Applied loads 表）</t>
         </is>
       </c>
       <c r="U10" t="n">
-        <v>1580000</v>
+        <v>438000</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>table of specimen cycles to failure.pdf（含 Total 行）</t>
+          <t>组内 L1-23.pdf（Applied loads 表）</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>蒙皮侧: 冲击中心 110.0, 60</t>
+          <t>30, 45 (脱粘)</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>FBG 分块快照(3071 个)</t>
+          <t>FBG 脚空间段 L(845, 1045) / R(2720, 2920); 含 LUNA DFOS</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>L1-27</t>
+          <t>L1-24</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>L1 谱载+FBG</t>
+          <t>L1 变幅VA+FBG</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1606,19 +1606,19 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="M11" t="n">
-        <v>1020</v>
+        <v>2</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>每 7 分钟 20 秒快照（全天覆盖，占空约 5%）</t>
+          <t>连续长记录</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>+8</t>
+          <t>+0</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1633,42 +1633,42 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>10 J</t>
+          <t>7.37 J</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>-50.4/-69 → -50.4/-78</t>
+          <t>-4/-40 → -4.5/-45 → -5/-50 → -5.5/-55 → -6/-60</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>291,000 + 238,000</t>
+          <t>20,000 + 75,000 + 25,000 + 62,000 + 60,000</t>
         </is>
       </c>
       <c r="U11" t="n">
-        <v>529000</v>
+        <v>242000</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>table of specimen cycles to failure.pdf（含 Total 行）</t>
+          <t>tables of cycles variable.pdf（含 Total 行）</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>蒙皮侧: 冲击中心 105.0, 60</t>
+          <t>蒙皮侧: 冲击中心 115.0, 165; 传感器编号 反向（L5R1…L1R5）</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>FBG 分块快照(1020 个)</t>
+          <t>FBG 连续长记录</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>L1-29</t>
+          <t>L1-25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1698,18 +1698,18 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>.dta×1</t>
+          <t>.dta×2</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>单段</t>
+          <t>分次加载（2 段，最长间隔 34 天）</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1721,7 +1721,7 @@
         <v>10</v>
       </c>
       <c r="M12" t="n">
-        <v>3105</v>
+        <v>3071</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1750,16 +1750,16 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>-50.4/-78 → -50.4/-78 → -55.2/-78 → -55.2/-82</t>
+          <t>-50.4/-75 → -50.4/-78</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>60,000(pristine) + 240,000(impact 10 J) + 300,000 + 600,000</t>
+          <t>1,000,000 + 580,000</t>
         </is>
       </c>
       <c r="U12" t="n">
-        <v>1300000</v>
+        <v>1580000</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -1768,19 +1768,19 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>蒙皮侧: 冲击中心 105.0, 60</t>
+          <t>蒙皮侧: 冲击中心 110.0, 60</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>FBG 分块快照(3105 个)</t>
+          <t>FBG 分块快照(3071 个)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>L1-30</t>
+          <t>L1-27</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1810,18 +1810,18 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>.dta×2</t>
+          <t>.dta×1</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>同一加载期连续采集（2 卷，最长停顿 19.7 小时）</t>
+          <t>单段</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1833,7 +1833,7 @@
         <v>10</v>
       </c>
       <c r="M13" t="n">
-        <v>27</v>
+        <v>1020</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1857,21 +1857,21 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>~10 J</t>
+          <t>10 J</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>-45.9/-78 → -45.9/-78</t>
+          <t>-50.4/-69 → -50.4/-78</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>10,000(pristine) + 150(impact)</t>
+          <t>291,000 + 238,000</t>
         </is>
       </c>
       <c r="U13" t="n">
-        <v>10150</v>
+        <v>529000</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -1885,14 +1885,14 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>FBG 分块快照(27 个)</t>
+          <t>FBG 分块快照(1020 个)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>L1-31</t>
+          <t>L1-29</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1922,18 +1922,18 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>.dta×2</t>
+          <t>.dta×1</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>分次加载（2 段，最长间隔 23 天）</t>
+          <t>单段</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1945,7 +1945,7 @@
         <v>10</v>
       </c>
       <c r="M14" t="n">
-        <v>2420</v>
+        <v>3105</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -1974,16 +1974,16 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>-50.4/-75 → -50.4/-78</t>
+          <t>-50.4/-78 → -50.4/-78 → -55.2/-78 → -55.2/-82</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>500,000 + 466,000</t>
+          <t>60,000(pristine) + 240,000(impact 10 J) + 300,000 + 600,000</t>
         </is>
       </c>
       <c r="U14" t="n">
-        <v>966000</v>
+        <v>1300000</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -1992,19 +1992,19 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>蒙皮侧: 冲击中心 60.0, 65</t>
+          <t>蒙皮侧: 冲击中心 105.0, 60</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>FBG 分块快照(2420 个)</t>
+          <t>FBG 分块快照(3105 个)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>L1-34</t>
+          <t>L1-30</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2034,18 +2034,18 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>.dta×1</t>
+          <t>.dta×2</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>单段</t>
+          <t>同一加载期连续采集（2 卷，最长停顿 19.7 小时）</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -2057,7 +2057,7 @@
         <v>10</v>
       </c>
       <c r="M15" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -2081,21 +2081,21 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>15 J</t>
+          <t>~10 J</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>-45.9/-78</t>
+          <t>-45.9/-78 → -45.9/-78</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1,400</t>
+          <t>10,000(pristine) + 150(impact)</t>
         </is>
       </c>
       <c r="U15" t="n">
-        <v>1400</v>
+        <v>10150</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -2104,19 +2104,19 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>蒙皮侧: 冲击中心 60.0, 180</t>
+          <t>蒙皮侧: 冲击中心 105.0, 60</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>FBG 连续长记录</t>
+          <t>FBG 分块快照(27 个)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>L1-35</t>
+          <t>L1-31</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2146,18 +2146,18 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>.dta×8</t>
+          <t>.dta×2</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I16" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>同一加载期多段采集（8 段，最长停顿 1.7 天）</t>
+          <t>分次加载（2 段，最长间隔 23 天）</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -2169,7 +2169,7 @@
         <v>10</v>
       </c>
       <c r="M16" t="n">
-        <v>1779</v>
+        <v>2420</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -2193,21 +2193,21 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>12.3 J</t>
+          <t>10 J</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>-45.9/-64.5 → -45.9/-69 → -45.9/-75 → -50.5/-75 → -50.4/-78</t>
+          <t>-50.4/-75 → -50.4/-78</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>247,000 + 92,000 + 10,000 + 73,000 + 30,000</t>
+          <t>500,000 + 466,000</t>
         </is>
       </c>
       <c r="U16" t="n">
-        <v>452000</v>
+        <v>966000</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -2216,19 +2216,19 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>蒙皮侧: 冲击中心 60.0, 70</t>
+          <t>蒙皮侧: 冲击中心 60.0, 65</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>FBG 分块快照(1779 个)</t>
+          <t>FBG 分块快照(2420 个)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>L1-36</t>
+          <t>L1-34</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2281,7 +2281,7 @@
         <v>10</v>
       </c>
       <c r="M17" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>10 J</t>
+          <t>15 J</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2315,11 +2315,11 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>4,500</t>
+          <t>1,400</t>
         </is>
       </c>
       <c r="U17" t="n">
-        <v>4500</v>
+        <v>1400</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -2328,19 +2328,19 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>蒙皮侧: 冲击中心 105.0, 60</t>
+          <t>蒙皮侧: 冲击中心 60.0, 180</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>FBG 分块快照(10 个)</t>
+          <t>FBG 连续长记录</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>L1-41</t>
+          <t>L1-35</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2370,18 +2370,18 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>.dta×1</t>
+          <t>.dta×8</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>单段</t>
+          <t>同一加载期多段采集（8 段，最长停顿 1.7 天）</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2393,7 +2393,7 @@
         <v>10</v>
       </c>
       <c r="M18" t="n">
-        <v>2688</v>
+        <v>1779</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -2417,21 +2417,21 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>预置脱粘 D20x20（无冲击）</t>
+          <t>12.3 J</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>-45.9/-64.5 → -45.9/-78</t>
+          <t>-45.9/-64.5 → -45.9/-69 → -45.9/-75 → -50.5/-75 → -50.4/-78</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>845,000 + 1,000,000</t>
+          <t>247,000 + 92,000 + 10,000 + 73,000 + 30,000</t>
         </is>
       </c>
       <c r="U18" t="n">
-        <v>1820000</v>
+        <v>452000</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
@@ -2440,19 +2440,19 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>蒙皮侧: 脱粘下缘 82.5, 160-180</t>
+          <t>蒙皮侧: 冲击中心 60.0, 70</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>FBG 分块快照(2688 个)</t>
+          <t>FBG 分块快照(1779 个)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>L1-44</t>
+          <t>L1-36</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2482,18 +2482,18 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>.dta×3</t>
+          <t>.dta×1</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>同一加载期连续采集（3 卷，最长停顿 1.0 小时）</t>
+          <t>单段</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2505,11 +2505,11 @@
         <v>10</v>
       </c>
       <c r="M19" t="n">
-        <v>1849</v>
+        <v>10</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>连续长记录</t>
+          <t>每 7 分钟 20 秒快照（全天覆盖，占空约 5%）</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -2529,21 +2529,21 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>预置脱粘 D25x20（无冲击）</t>
+          <t>10 J</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>-55.2/-78 → -45.9/-59.7</t>
+          <t>-45.9/-78</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>460 + 1,160,000</t>
+          <t>4,500</t>
         </is>
       </c>
       <c r="U19" t="n">
-        <v>1160000</v>
+        <v>4500</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
@@ -2552,49 +2552,49 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>蒙皮侧: 脱粘下缘 60.0, 60-85</t>
+          <t>蒙皮侧: 冲击中心 105.0, 60</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>FBG 分块快照(1849 个)</t>
+          <t>FBG 分块快照(10 个)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>L1-49</t>
+          <t>L1-41</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>既有</t>
+          <t>新增</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>L1 恒幅+DFOS</t>
+          <t>L1 谱载+FBG</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t>有</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>有</t>
-        </is>
-      </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>.pridb×1</t>
+          <t>.dta×1</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -2610,22 +2610,30 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>10</v>
+      </c>
+      <c r="M20" t="n">
+        <v>2688</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>每 7 分钟 20 秒快照（全天覆盖，占空约 5%）</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>+8</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
           <t>无</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>+0</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>有</t>
-        </is>
-      </c>
       <c r="Q20" t="inlineStr">
         <is>
           <t>无</t>
@@ -2633,103 +2641,111 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>10 J（组内统一）</t>
+          <t>预置脱粘 D20x20（无冲击）</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>-6.5/-65（组内统一）</t>
+          <t>-45.9/-64.5 → -45.9/-78</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>等幅，无分级</t>
+          <t>845,000 + 1,000,000</t>
         </is>
       </c>
       <c r="U20" t="n">
-        <v>43702</v>
+        <v>1820000</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>组内 L1-49.pdf（Applied loads 表）</t>
+          <t>table of specimen cycles to failure.pdf（含 Total 行）</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>加筋条侧: 冲击中心 115.0, 160</t>
+          <t>蒙皮侧: 脱粘下缘 82.5, 160-180</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>FBG 脚空间段 L(2835, 2977) / R(826, 966); 含 LUNA DFOS</t>
+          <t>FBG 分块快照(2688 个)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>L1-50</t>
+          <t>L1-44</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>既有</t>
+          <t>新增</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>L1 恒幅+DFOS</t>
+          <t>L1 谱载+FBG</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
           <t>有</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>.dta×3</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>3</v>
+      </c>
+      <c r="I21" t="n">
+        <v>3</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>同一加载期连续采集（3 卷，最长停顿 1.0 小时）</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
         <is>
           <t>有</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>.pridb×1</t>
-        </is>
-      </c>
-      <c r="H21" t="n">
-        <v>1</v>
-      </c>
-      <c r="I21" t="n">
-        <v>1</v>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>单段</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
+      <c r="L21" t="n">
+        <v>10</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1849</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>连续长记录</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>+8</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>+0</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>有</t>
-        </is>
-      </c>
       <c r="Q21" t="inlineStr">
         <is>
           <t>无</t>
@@ -2737,42 +2753,42 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>10 J（组内统一）</t>
+          <t>预置脱粘 D25x20（无冲击）</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>-6.5/-65（组内统一）</t>
+          <t>-55.2/-78 → -45.9/-59.7</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>等幅，无分级</t>
+          <t>460 + 1,160,000</t>
         </is>
       </c>
       <c r="U21" t="n">
-        <v>60500</v>
+        <v>1160000</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>组内 L1-50.pdf（Applied loads 表）</t>
+          <t>table of specimen cycles to failure.pdf（含 Total 行）</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>加筋条侧: 冲击中心 115.0, 160</t>
+          <t>蒙皮侧: 脱粘下缘 60.0, 60-85</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>FBG 脚空间段 L(3121, 3263) / R(903, 1046); 含 LUNA DFOS</t>
+          <t>FBG 分块快照(1849 个)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>L1-51</t>
+          <t>L1-49</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2855,11 +2871,11 @@
         </is>
       </c>
       <c r="U22" t="n">
-        <v>89431</v>
+        <v>43702</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>组内 L1-51.pdf（Applied loads 表）</t>
+          <t>组内 L1-49.pdf（Applied loads 表）</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
@@ -2869,14 +2885,14 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>FBG 脚空间段 L(3046, 3190) / R(736, 879); 含 LUNA DFOS</t>
+          <t>FBG 脚空间段 L(2835, 2977) / R(826, 966); 含 LUNA DFOS</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>L1-52</t>
+          <t>L1-50</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2959,11 +2975,11 @@
         </is>
       </c>
       <c r="U23" t="n">
-        <v>368558</v>
+        <v>60500</v>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>组内 L1-52.pdf（Applied loads 表）</t>
+          <t>组内 L1-50.pdf（Applied loads 表）</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
@@ -2973,14 +2989,14 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>FBG 脚空间段 L(1298, 1439) / R(3810, 4140); 含 LUNA DFOS</t>
+          <t>FBG 脚空间段 L(3121, 3263) / R(903, 1046); 含 LUNA DFOS</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>L1-54</t>
+          <t>L1-51</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3063,11 +3079,11 @@
         </is>
       </c>
       <c r="U24" t="n">
-        <v>510961</v>
+        <v>89431</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>组内 L1-54.pdf（Applied loads 表）</t>
+          <t>组内 L1-51.pdf（Applied loads 表）</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
@@ -3077,14 +3093,14 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>FBG 脚空间段 L(3292, 3431) / R(916, 1056); 含 LUNA DFOS</t>
+          <t>FBG 脚空间段 L(3046, 3190) / R(736, 879); 含 LUNA DFOS</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>L1-55</t>
+          <t>L1-52</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3167,28 +3183,28 @@
         </is>
       </c>
       <c r="U25" t="n">
-        <v>221356</v>
+        <v>368558</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>组内 L1-55.pdf（Applied loads 表）</t>
+          <t>组内 L1-52.pdf（Applied loads 表）</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>加筋条侧: 冲击中心 50.0, 80</t>
+          <t>加筋条侧: 冲击中心 115.0, 160</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>FBG 脚空间段 L(3088, 3229) / R(869, 1011); 含 LUNA DFOS</t>
+          <t>FBG 脚空间段 L(1298, 1439) / R(3810, 4140); 含 LUNA DFOS</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>L1-56</t>
+          <t>L1-54</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3271,11 +3287,11 @@
         </is>
       </c>
       <c r="U26" t="n">
-        <v>751226</v>
+        <v>510961</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>组内 L1-56.pdf（Applied loads 表）</t>
+          <t>组内 L1-54.pdf（Applied loads 表）</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
@@ -3285,14 +3301,14 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>FBG 脚空间段 L(3073, 3210) / R(919, 1058); 含 LUNA DFOS</t>
+          <t>FBG 脚空间段 L(3292, 3431) / R(916, 1056); 含 LUNA DFOS</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>L1-59</t>
+          <t>L1-55</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3322,18 +3338,18 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>.pridb×2</t>
+          <t>.pridb×1</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>同一采集、DAQ 按卷续写（2 卷，内容不重复）</t>
+          <t>单段</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -3375,28 +3391,28 @@
         </is>
       </c>
       <c r="U27" t="n">
-        <v>105137</v>
+        <v>221356</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>组内 L1-59.pdf（Applied loads 表）</t>
+          <t>组内 L1-55.pdf（Applied loads 表）</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>加筋条侧: 冲击中心 115.0, 160</t>
+          <t>加筋条侧: 冲击中心 50.0, 80</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>FBG 脚空间段 L(3106, 3246) / R(907, 1049); 含 LUNA DFOS</t>
+          <t>FBG 脚空间段 L(3088, 3229) / R(869, 1011); 含 LUNA DFOS</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>L1-60</t>
+          <t>L1-56</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3479,19 +3495,227 @@
         </is>
       </c>
       <c r="U28" t="n">
+        <v>751226</v>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>组内 L1-56.pdf（Applied loads 表）</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>加筋条侧: 冲击中心 115.0, 160</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>FBG 脚空间段 L(3073, 3210) / R(919, 1058); 含 LUNA DFOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>L1-59</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>既有</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>L1 恒幅+DFOS</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>.pridb×2</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>2</v>
+      </c>
+      <c r="I29" t="n">
+        <v>2</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>同一采集、DAQ 按卷续写（2 卷，内容不重复）</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>+0</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>10 J（组内统一）</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>-6.5/-65（组内统一）</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>等幅，无分级</t>
+        </is>
+      </c>
+      <c r="U29" t="n">
+        <v>105137</v>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>组内 L1-59.pdf（Applied loads 表）</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>加筋条侧: 冲击中心 115.0, 160</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>FBG 脚空间段 L(3106, 3246) / R(907, 1049); 含 LUNA DFOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>L1-60</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>既有</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>L1 恒幅+DFOS</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>.pridb×1</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>单段</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>+0</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>10 J（组内统一）</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>-6.5/-65（组内统一）</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>等幅，无分级</t>
+        </is>
+      </c>
+      <c r="U30" t="n">
         <v>165884</v>
       </c>
-      <c r="V28" t="inlineStr">
+      <c r="V30" t="inlineStr">
         <is>
           <t>组内 L1-60.pdf（Applied loads 表）</t>
         </is>
       </c>
-      <c r="W28" t="inlineStr">
+      <c r="W30" t="inlineStr">
         <is>
           <t>加筋条侧: 冲击中心 50.0, 80</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
+      <c r="X30" t="inlineStr">
         <is>
           <t>FBG 脚空间段 L(3013, 3153) / R(822, 964); 含 LUNA DFOS</t>
         </is>
@@ -3571,7 +3795,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>L1-03 L1-04 L1-05 L1-09</t>
+          <t>L1-03 L1-04 L1-05 L1-09 L1-23</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -3665,7 +3889,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>L1-06 L1-13 L1-14 L1-24</t>
+          <t>L1-06 L1-13 L1-14 L1-24 L1-22</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -3757,7 +3981,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F72"/>
+  <dimension ref="A1:F78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4411,7 +4635,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>L1-24</t>
+          <t>L1-22</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -4425,21 +4649,21 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E24" t="n">
-        <v>197.3</v>
+        <v>19762.7</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>.dta×1</t>
+          <t>.dta×11</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>L1-24</t>
+          <t>L1-22</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -4456,7 +4680,7 @@
         <v>2</v>
       </c>
       <c r="E25" t="n">
-        <v>67.8</v>
+        <v>65</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -4467,12 +4691,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>L1-25</t>
+          <t>L1-23</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>L1 谱载+FBG</t>
+          <t>L1 恒幅+FBG+DFOS</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -4481,26 +4705,26 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>420.7</v>
+        <v>1770.9</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>.dta×2</t>
+          <t>.pridb×1</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>L1-25</t>
+          <t>L1-23</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>L1 谱载+FBG</t>
+          <t>L1 恒幅+FBG+DFOS</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -4509,82 +4733,82 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>3071</v>
+        <v>5</v>
       </c>
       <c r="E27" t="n">
-        <v>138.3</v>
+        <v>168.2</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>.txt×3071</t>
+          <t>.txt×5</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>L1-27</t>
+          <t>L1-23</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>L1 谱载+FBG</t>
+          <t>L1 恒幅+FBG+DFOS</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>LUNA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28" t="n">
-        <v>1128.9</v>
+        <v>58.6</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>.dta×1</t>
+          <t>.txt×2</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>L1-27</t>
+          <t>L1-23</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>L1 谱载+FBG</t>
+          <t>L1 恒幅+FBG+DFOS</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>FBG</t>
+          <t>(组根)</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1020</v>
+        <v>4</v>
       </c>
       <c r="E29" t="n">
-        <v>46.2</v>
+        <v>4415.4</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>.txt×1020</t>
+          <t>.csv×3, .pdf×1</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>L1-29</t>
+          <t>L1-24</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>L1 谱载+FBG</t>
+          <t>L1 变幅VA+FBG</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4596,7 +4820,7 @@
         <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>395.1</v>
+        <v>197.3</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4607,12 +4831,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>L1-29</t>
+          <t>L1-24</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>L1 谱载+FBG</t>
+          <t>L1 变幅VA+FBG</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4621,21 +4845,21 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>3105</v>
+        <v>2</v>
       </c>
       <c r="E31" t="n">
-        <v>101.6</v>
+        <v>67.8</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>.txt×3105</t>
+          <t>.txt×2</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>L1-30</t>
+          <t>L1-25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4652,7 +4876,7 @@
         <v>2</v>
       </c>
       <c r="E32" t="n">
-        <v>0.8</v>
+        <v>420.7</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4663,7 +4887,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>L1-30</t>
+          <t>L1-25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4677,21 +4901,21 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>27</v>
+        <v>3071</v>
       </c>
       <c r="E33" t="n">
-        <v>1.3</v>
+        <v>138.3</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>.txt×27</t>
+          <t>.txt×3071</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>L1-31</t>
+          <t>L1-27</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4705,21 +4929,21 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E34" t="n">
-        <v>726.8</v>
+        <v>1128.9</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>.dta×2</t>
+          <t>.dta×1</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>L1-31</t>
+          <t>L1-27</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4733,21 +4957,21 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>2420</v>
+        <v>1020</v>
       </c>
       <c r="E35" t="n">
-        <v>107.8</v>
+        <v>46.2</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>.txt×2420</t>
+          <t>.txt×1020</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>L1-34</t>
+          <t>L1-29</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4764,7 +4988,7 @@
         <v>1</v>
       </c>
       <c r="E36" t="n">
-        <v>1.5</v>
+        <v>395.1</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4775,7 +4999,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>L1-34</t>
+          <t>L1-29</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4789,21 +5013,21 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>2</v>
+        <v>3105</v>
       </c>
       <c r="E37" t="n">
-        <v>0.1</v>
+        <v>101.6</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>.txt×2</t>
+          <t>.txt×3105</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>L1-35</t>
+          <t>L1-30</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4817,21 +5041,21 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E38" t="n">
-        <v>901.3</v>
+        <v>0.8</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>.dta×8</t>
+          <t>.dta×2</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>L1-35</t>
+          <t>L1-30</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4845,21 +5069,21 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1779</v>
+        <v>27</v>
       </c>
       <c r="E39" t="n">
-        <v>81.90000000000001</v>
+        <v>1.3</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>.txt×1779</t>
+          <t>.txt×27</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>L1-36</t>
+          <t>L1-31</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4873,21 +5097,21 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E40" t="n">
-        <v>10.2</v>
+        <v>726.8</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>.dta×1</t>
+          <t>.dta×2</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>L1-36</t>
+          <t>L1-31</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4901,21 +5125,21 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>10</v>
+        <v>2420</v>
       </c>
       <c r="E41" t="n">
-        <v>0.4</v>
+        <v>107.8</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>.txt×10</t>
+          <t>.txt×2420</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>L1-41</t>
+          <t>L1-34</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4932,7 +5156,7 @@
         <v>1</v>
       </c>
       <c r="E42" t="n">
-        <v>217</v>
+        <v>1.5</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4943,7 +5167,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>L1-41</t>
+          <t>L1-34</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4957,21 +5181,21 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>2688</v>
+        <v>2</v>
       </c>
       <c r="E43" t="n">
-        <v>119</v>
+        <v>0.1</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>.txt×2688</t>
+          <t>.txt×2</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>L1-44</t>
+          <t>L1-35</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4985,21 +5209,21 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E44" t="n">
-        <v>3456.2</v>
+        <v>901.3</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>.dta×3</t>
+          <t>.dta×8</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>L1-44</t>
+          <t>L1-35</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5013,26 +5237,26 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1849</v>
+        <v>1779</v>
       </c>
       <c r="E45" t="n">
-        <v>111</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>.txt×1849</t>
+          <t>.txt×1779</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>L1-49</t>
+          <t>L1-36</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>L1 恒幅+DFOS</t>
+          <t>L1 谱载+FBG</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -5044,158 +5268,158 @@
         <v>1</v>
       </c>
       <c r="E46" t="n">
-        <v>285.6</v>
+        <v>10.2</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>.pridb×1</t>
+          <t>.dta×1</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>L1-49</t>
+          <t>L1-36</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>L1 恒幅+DFOS</t>
+          <t>L1 谱载+FBG</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>LUNA</t>
+          <t>FBG</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E47" t="n">
-        <v>117.7</v>
+        <v>0.4</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>.txt×2</t>
+          <t>.txt×10</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>L1-49</t>
+          <t>L1-41</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>L1 恒幅+DFOS</t>
+          <t>L1 谱载+FBG</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>(组根)</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E48" t="n">
-        <v>4.7</v>
+        <v>217</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>.csv×5, .pdf×1</t>
+          <t>.dta×1</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>L1-50</t>
+          <t>L1-41</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>L1 恒幅+DFOS</t>
+          <t>L1 谱载+FBG</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>FBG</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1</v>
+        <v>2688</v>
       </c>
       <c r="E49" t="n">
-        <v>210.5</v>
+        <v>119</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>.pridb×1</t>
+          <t>.txt×2688</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>L1-50</t>
+          <t>L1-44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>L1 恒幅+DFOS</t>
+          <t>L1 谱载+FBG</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>LUNA</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="D50" t="n">
         <v>3</v>
       </c>
       <c r="E50" t="n">
-        <v>541.6</v>
+        <v>3456.2</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>.txt×3</t>
+          <t>.dta×3</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>L1-50</t>
+          <t>L1-44</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>L1 恒幅+DFOS</t>
+          <t>L1 谱载+FBG</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>(组根)</t>
+          <t>FBG</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>6</v>
+        <v>1849</v>
       </c>
       <c r="E51" t="n">
-        <v>5.9</v>
+        <v>111</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>.csv×5, .pdf×1</t>
+          <t>.txt×1849</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>L1-51</t>
+          <t>L1-49</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5212,7 +5436,7 @@
         <v>1</v>
       </c>
       <c r="E52" t="n">
-        <v>521.5</v>
+        <v>285.6</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5223,7 +5447,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>L1-51</t>
+          <t>L1-49</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5240,7 +5464,7 @@
         <v>2</v>
       </c>
       <c r="E53" t="n">
-        <v>963.9</v>
+        <v>117.7</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5251,7 +5475,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>L1-51</t>
+          <t>L1-49</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5268,7 +5492,7 @@
         <v>6</v>
       </c>
       <c r="E54" t="n">
-        <v>11.5</v>
+        <v>4.7</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5279,7 +5503,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>L1-52</t>
+          <t>L1-50</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5296,7 +5520,7 @@
         <v>1</v>
       </c>
       <c r="E55" t="n">
-        <v>1426</v>
+        <v>210.5</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5307,7 +5531,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>L1-52</t>
+          <t>L1-50</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5321,21 +5545,21 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E56" t="n">
-        <v>4325.7</v>
+        <v>541.6</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>.txt×1</t>
+          <t>.txt×3</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>L1-52</t>
+          <t>L1-50</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5352,7 +5576,7 @@
         <v>6</v>
       </c>
       <c r="E57" t="n">
-        <v>33</v>
+        <v>5.9</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5363,7 +5587,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>L1-54</t>
+          <t>L1-51</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5380,7 +5604,7 @@
         <v>1</v>
       </c>
       <c r="E58" t="n">
-        <v>2196.1</v>
+        <v>521.5</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5391,7 +5615,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>L1-54</t>
+          <t>L1-51</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5405,21 +5629,21 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E59" t="n">
-        <v>5363.3</v>
+        <v>963.9</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>.txt×1</t>
+          <t>.txt×2</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>L1-54</t>
+          <t>L1-51</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5436,7 +5660,7 @@
         <v>6</v>
       </c>
       <c r="E60" t="n">
-        <v>47</v>
+        <v>11.5</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5447,7 +5671,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>L1-55</t>
+          <t>L1-52</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5464,7 +5688,7 @@
         <v>1</v>
       </c>
       <c r="E61" t="n">
-        <v>456.9</v>
+        <v>1426</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5475,7 +5699,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>L1-55</t>
+          <t>L1-52</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5489,21 +5713,21 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>2214.9</v>
+        <v>4325.7</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>.txt×3</t>
+          <t>.txt×1</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>L1-55</t>
+          <t>L1-52</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5520,7 +5744,7 @@
         <v>6</v>
       </c>
       <c r="E63" t="n">
-        <v>19.1</v>
+        <v>33</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5531,7 +5755,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>L1-56</t>
+          <t>L1-54</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5548,7 +5772,7 @@
         <v>1</v>
       </c>
       <c r="E64" t="n">
-        <v>2532</v>
+        <v>2196.1</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5559,7 +5783,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>L1-56</t>
+          <t>L1-54</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5573,21 +5797,21 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>1883.8</v>
+        <v>5363.3</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>.txt×2</t>
+          <t>.txt×1</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>L1-56</t>
+          <t>L1-54</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5604,7 +5828,7 @@
         <v>6</v>
       </c>
       <c r="E66" t="n">
-        <v>25.6</v>
+        <v>47</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5615,7 +5839,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>L1-59</t>
+          <t>L1-55</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5629,21 +5853,21 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E67" t="n">
-        <v>510.1</v>
+        <v>456.9</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>.pridb×2</t>
+          <t>.pridb×1</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>L1-59</t>
+          <t>L1-55</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5660,7 +5884,7 @@
         <v>3</v>
       </c>
       <c r="E68" t="n">
-        <v>1042.7</v>
+        <v>2214.9</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5671,7 +5895,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>L1-59</t>
+          <t>L1-55</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5688,7 +5912,7 @@
         <v>6</v>
       </c>
       <c r="E69" t="n">
-        <v>10</v>
+        <v>19.1</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5699,7 +5923,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>L1-60</t>
+          <t>L1-56</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5716,7 +5940,7 @@
         <v>1</v>
       </c>
       <c r="E70" t="n">
-        <v>963.9</v>
+        <v>2532</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5727,7 +5951,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>L1-60</t>
+          <t>L1-56</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5744,7 +5968,7 @@
         <v>2</v>
       </c>
       <c r="E71" t="n">
-        <v>1658.7</v>
+        <v>1883.8</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5755,7 +5979,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>L1-60</t>
+          <t>L1-56</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5772,9 +5996,177 @@
         <v>6</v>
       </c>
       <c r="E72" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>.csv×5, .pdf×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>L1-59</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>L1 恒幅+DFOS</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>2</v>
+      </c>
+      <c r="E73" t="n">
+        <v>510.1</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>.pridb×2</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>L1-59</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>L1 恒幅+DFOS</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>LUNA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>3</v>
+      </c>
+      <c r="E74" t="n">
+        <v>1042.7</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>.txt×3</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>L1-59</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>L1 恒幅+DFOS</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>(组根)</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>6</v>
+      </c>
+      <c r="E75" t="n">
+        <v>10</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>.csv×5, .pdf×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>L1-60</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>L1 恒幅+DFOS</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>1</v>
+      </c>
+      <c r="E76" t="n">
+        <v>963.9</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>.pridb×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>L1-60</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>L1 恒幅+DFOS</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>LUNA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>2</v>
+      </c>
+      <c r="E77" t="n">
+        <v>1658.7</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>.txt×2</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>L1-60</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>L1 恒幅+DFOS</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>(组根)</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>6</v>
+      </c>
+      <c r="E78" t="n">
         <v>15.3</v>
       </c>
-      <c r="F72" t="inlineStr">
+      <c r="F78" t="inlineStr">
         <is>
           <t>.csv×5, .pdf×1</t>
         </is>
@@ -5791,7 +6183,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I63"/>
+  <dimension ref="A1:I77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6381,7 +6773,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>L1-24</t>
+          <t>L1-22</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -6396,25 +6788,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>L1-24.DTA</t>
+          <t>L1-22_1.DTA</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>197.3</v>
+        <v>1906.4</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tue May 12 12:58:08 2020</t>
+          <t>Thu May 07 10:09:56 2020</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-09-29 19:44</t>
+          <t>2020-05-08 23:05</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2020-05-12 12:58</t>
+          <t>2020-05-07 10:09</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -6426,7 +6818,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>L1-24</t>
+          <t>L1-22</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -6436,28 +6828,42 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>FBG 窗口</t>
+          <t>AE 采集段</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2020-05-09 → 2020-05-09（1 天）</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
+          <t>L1-22_10.DTA</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1906.4</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Thu May 07 10:09:56 2020</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2020-05-11 10:14</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2020-05-07 10:09</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>连续长记录；2 个分块</t>
+          <t>与上一卷同一采集启动时刻（DAQ 按卷续写，内容不重复）</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>L1-24</t>
+          <t>L1-22</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -6467,33 +6873,47 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>FBG 窗口</t>
+          <t>AE 采集段</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2020-05-12 → 2020-05-12（1 天）</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
+          <t>L1-22_11.DTA</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>698.5</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Thu May 07 10:09:56 2020</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2020-05-11 11:04</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>2020-05-07 10:09</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>连续长记录；2 个分块</t>
+          <t>与上一卷同一采集启动时刻（DAQ 按卷续写，内容不重复）</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>L1-25</t>
+          <t>L1-22</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>L1 谱载+FBG</t>
+          <t>L1 变幅VA+FBG</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -6503,42 +6923,42 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>L1-25-1.DTA</t>
+          <t>L1-22_2.DTA</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>246</v>
+        <v>1906.4</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Wed Aug 26 12:04:11 2020</t>
+          <t>Thu May 07 10:09:56 2020</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2020-09-05 15:46</t>
+          <t>2020-05-09 19:37</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2020-09-03 12:04</t>
+          <t>2020-05-07 10:09</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>首段</t>
+          <t>与上一卷同一采集启动时刻（DAQ 按卷续写，内容不重复）</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>L1-25</t>
+          <t>L1-22</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>L1 谱载+FBG</t>
+          <t>L1 变幅VA+FBG</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -6548,104 +6968,132 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>L1-25-2.DTA</t>
+          <t>L1-22_3.DTA</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>174.6</v>
+        <v>1906.4</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tue Sep 29 16:07:27 2020</t>
+          <t>Thu May 07 10:09:56 2020</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2020-10-04 10:50</t>
+          <t>2020-05-10 08:52</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2020-10-07 16:07</t>
+          <t>2020-05-07 10:09</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>距上一段 34 天（推断为另一次加载）</t>
+          <t>与上一卷同一采集启动时刻（DAQ 按卷续写，内容不重复）</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>L1-25</t>
+          <t>L1-22</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>L1 谱载+FBG</t>
+          <t>L1 变幅VA+FBG</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>FBG 窗口</t>
+          <t>AE 采集段</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2020-09-03 → 2020-09-13（11 天）</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
+          <t>L1-22_4.DTA</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>1906.4</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Thu May 07 10:09:56 2020</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2020-05-10 15:45</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>2020-05-07 10:09</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>每 7 分钟 20 秒快照（全天覆盖，占空约 5%）；3071 个分块</t>
+          <t>与上一卷同一采集启动时刻（DAQ 按卷续写，内容不重复）</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>L1-25</t>
+          <t>L1-22</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>L1 谱载+FBG</t>
+          <t>L1 变幅VA+FBG</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>FBG 窗口</t>
+          <t>AE 采集段</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2020-10-07 → 2020-10-12（6 天）</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
+          <t>L1-22_5.DTA</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>1906.5</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Thu May 07 10:09:56 2020</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2020-05-10 20:29</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>2020-05-07 10:09</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>每 7 分钟 20 秒快照（全天覆盖，占空约 5%）；3071 个分块</t>
+          <t>与上一卷同一采集启动时刻（DAQ 按卷续写，内容不重复）</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>L1-27</t>
+          <t>L1-22</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>L1 谱载+FBG</t>
+          <t>L1 变幅VA+FBG</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -6655,73 +7103,87 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>L1-27.DTA</t>
+          <t>L1-22_6.DTA</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1128.9</v>
+        <v>1906.4</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fri Jul 17 11:19:05 2020</t>
+          <t>Thu May 07 10:09:56 2020</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2020-07-22 11:27</t>
+          <t>2020-05-10 23:48</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2020-07-25 11:19</t>
+          <t>2020-05-07 10:09</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>首段</t>
+          <t>与上一卷同一采集启动时刻（DAQ 按卷续写，内容不重复）</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>L1-27</t>
+          <t>L1-22</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>L1 谱载+FBG</t>
+          <t>L1 变幅VA+FBG</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>FBG 窗口</t>
+          <t>AE 采集段</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2020-07-25 → 2020-07-30（6 天）</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
+          <t>L1-22_7.DTA</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>1906.4</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Thu May 07 10:09:56 2020</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2020-05-11 03:13</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>2020-05-07 10:09</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>每 7 分钟 20 秒快照（全天覆盖，占空约 5%）；1020 个分块</t>
+          <t>与上一卷同一采集启动时刻（DAQ 按卷续写，内容不重复）</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>L1-29</t>
+          <t>L1-22</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>L1 谱载+FBG</t>
+          <t>L1 变幅VA+FBG</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -6731,118 +7193,118 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>L1-29.DTA</t>
+          <t>L1-22_8.DTA</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>395.1</v>
+        <v>1906.5</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sun Sep 13 11:48:18 2020</t>
+          <t>Thu May 07 10:09:56 2020</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2020-09-28 16:38</t>
+          <t>2020-05-11 06:00</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2020-09-21 11:48</t>
+          <t>2020-05-07 10:09</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>首段</t>
+          <t>与上一卷同一采集启动时刻（DAQ 按卷续写，内容不重复）</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>L1-29</t>
+          <t>L1-22</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>L1 谱载+FBG</t>
+          <t>L1 变幅VA+FBG</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>FBG 窗口</t>
+          <t>AE 采集段</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2020-09-21 → 2020-10-06（16 天）</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
+          <t>L1-22_9.DTA</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>1906.4</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Thu May 07 10:09:56 2020</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2020-05-11 08:20</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>2020-05-07 10:09</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>每 7 分钟 20 秒快照（全天覆盖，占空约 5%）；3105 个分块</t>
+          <t>与上一卷同一采集启动时刻（DAQ 按卷续写，内容不重复）</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>L1-30</t>
+          <t>L1-22</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>L1 谱载+FBG</t>
+          <t>L1 变幅VA+FBG</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AE 采集段</t>
+          <t>FBG 窗口</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>L1-30-1.DTA</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Wed Jul 08 16:30:38 2020</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>2020-07-08 18:12</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>2020-07-16 16:30</t>
-        </is>
-      </c>
+          <t>2020-05-07 → 2020-05-09（2 天）</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
-          <t>首段</t>
+          <t>连续长记录；2 个分块</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>L1-30</t>
+          <t>L1-23</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>L1 谱载+FBG</t>
+          <t>L1 恒幅+FBG+DFOS</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -6852,42 +7314,34 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>L1-30-2.DTA</t>
+          <t>L1-23.pridb</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Thu Jul 09 12:10:56 2020</t>
-        </is>
-      </c>
+        <v>1770.9</v>
+      </c>
+      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2020-07-09 12:27</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>2020-07-17 12:10</t>
-        </is>
-      </c>
+          <t>2009-11-16 13:04</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>与上一段接续（间隔 19.7 小时）</t>
+          <t>首段</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>L1-30</t>
+          <t>L1-23</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>L1 谱载+FBG</t>
+          <t>L1 恒幅+FBG+DFOS</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -6897,7 +7351,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2020-07-16 → 2020-07-17（2 天）</t>
+          <t>2019-11-29 → 2019-12-02（3 天）</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
@@ -6906,19 +7360,19 @@
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
-          <t>每 7 分钟 20 秒快照（全天覆盖，占空约 5%）；27 个分块</t>
+          <t>连续长记录；5 个分块</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>L1-31</t>
+          <t>L1-24</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>L1 谱载+FBG</t>
+          <t>L1 变幅VA+FBG</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -6928,25 +7382,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>L1-31-1.DTA</t>
+          <t>L1-24.DTA</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>190.9</v>
+        <v>197.3</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mon Jul 27 14:16:58 2020</t>
+          <t>Tue May 12 12:58:08 2020</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2020-08-01 03:11</t>
+          <t>2026-09-29 19:44</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2020-08-04 14:16</t>
+          <t>2020-05-12 12:58</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -6958,57 +7412,43 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>L1-31</t>
+          <t>L1-24</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>L1 谱载+FBG</t>
+          <t>L1 变幅VA+FBG</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>AE 采集段</t>
+          <t>FBG 窗口</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>L1-31-2.DTA</t>
-        </is>
-      </c>
-      <c r="E32" t="n">
-        <v>535.9</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Wed Aug 19 12:51:17 2020</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>2020-08-26 10:48</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>2020-08-27 12:51</t>
-        </is>
-      </c>
+          <t>2020-05-09 → 2020-05-09（1 天）</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
-          <t>距上一段 23 天（推断为另一次加载）</t>
+          <t>连续长记录；2 个分块</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>L1-31</t>
+          <t>L1-24</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>L1 谱载+FBG</t>
+          <t>L1 变幅VA+FBG</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -7018,7 +7458,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2020-08-04 → 2020-08-09（6 天）</t>
+          <t>2020-05-12 → 2020-05-12（1 天）</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
@@ -7027,14 +7467,14 @@
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
-          <t>每 7 分钟 20 秒快照（全天覆盖，占空约 5%）；2420 个分块</t>
+          <t>连续长记录；2 个分块</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>L1-31</t>
+          <t>L1-25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -7044,28 +7484,42 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>FBG 窗口</t>
+          <t>AE 采集段</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2020-08-27 → 2020-09-03（8 天）</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
+          <t>L1-25-1.DTA</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>246</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Wed Aug 26 12:04:11 2020</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2020-09-05 15:46</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>2020-09-03 12:04</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>每 7 分钟 20 秒快照（全天覆盖，占空约 5%）；2420 个分块</t>
+          <t>首段</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>L1-34</t>
+          <t>L1-25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -7080,37 +7534,37 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>L1-34.DTA</t>
+          <t>L1-25-2.DTA</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1.5</v>
+        <v>174.6</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Wed Jul 08 14:20:59 2020</t>
+          <t>Tue Sep 29 16:07:27 2020</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2020-07-08 14:33</t>
+          <t>2020-10-04 10:50</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2020-07-16 14:20</t>
+          <t>2020-10-07 16:07</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>首段</t>
+          <t>距上一段 34 天（推断为另一次加载）</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>L1-34</t>
+          <t>L1-25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -7125,7 +7579,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2020-07-16 → 2020-07-16（1 天）</t>
+          <t>2020-09-03 → 2020-09-13（11 天）</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
@@ -7134,14 +7588,14 @@
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
-          <t>每 7 分钟 20 秒快照（全天覆盖，占空约 5%）；2 个分块</t>
+          <t>每 7 分钟 20 秒快照（全天覆盖，占空约 5%）；3071 个分块</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>L1-35</t>
+          <t>L1-25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -7151,42 +7605,28 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>AE 采集段</t>
+          <t>FBG 窗口</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>L1-35-1.DTA</t>
-        </is>
-      </c>
-      <c r="E37" t="n">
-        <v>61.9</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Thu Jul 09 15:19:43 2020</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>2020-07-10 12:20</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>2020-07-17 15:19</t>
-        </is>
-      </c>
+          <t>2020-10-07 → 2020-10-12（6 天）</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
-          <t>首段</t>
+          <t>每 7 分钟 20 秒快照（全天覆盖，占空约 5%）；3071 个分块</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>L1-35</t>
+          <t>L1-27</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -7201,37 +7641,37 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>L1-35-2.DTA</t>
+          <t>L1-27.DTA</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>115.6</v>
+        <v>1128.9</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Fri Jul 10 12:21:07 2020</t>
+          <t>Fri Jul 17 11:19:05 2020</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2020-07-11 11:30</t>
+          <t>2020-07-22 11:27</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2020-07-18 12:21</t>
+          <t>2020-07-25 11:19</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>与上一段接续（间隔 21.0 小时）</t>
+          <t>首段</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>L1-35</t>
+          <t>L1-27</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -7241,42 +7681,28 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>AE 采集段</t>
+          <t>FBG 窗口</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>L1-35-3.DTA</t>
-        </is>
-      </c>
-      <c r="E39" t="n">
-        <v>37.3</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Sat Jul 11 11:32:49 2020</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>2020-07-11 19:41</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>2020-07-19 11:32</t>
-        </is>
-      </c>
+          <t>2020-07-25 → 2020-07-30（6 天）</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
-          <t>与上一段接续（间隔 23.2 小时）</t>
+          <t>每 7 分钟 20 秒快照（全天覆盖，占空约 5%）；1020 个分块</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>L1-35</t>
+          <t>L1-29</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -7291,37 +7717,37 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>L1-35-4.DTA</t>
+          <t>L1-29.DTA</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>158.8</v>
+        <v>395.1</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sat Jul 11 19:50:24 2020</t>
+          <t>Sun Sep 13 11:48:18 2020</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2020-07-12 11:25</t>
+          <t>2020-09-28 16:38</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2020-07-19 19:50</t>
+          <t>2020-09-21 11:48</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>与上一段接续（间隔 8.3 小时）</t>
+          <t>首段</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>L1-35</t>
+          <t>L1-29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -7331,42 +7757,28 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>AE 采集段</t>
+          <t>FBG 窗口</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>L1-35-5.DTA</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>202.9</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Mon Jul 13 12:21:51 2020</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>2020-07-14 16:00</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>2020-07-21 12:21</t>
-        </is>
-      </c>
+          <t>2020-09-21 → 2020-10-06（16 天）</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
-          <t>距上一段 1.7 天（同一加载期内的停机夜歇）</t>
+          <t>每 7 分钟 20 秒快照（全天覆盖，占空约 5%）；3105 个分块</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>L1-35</t>
+          <t>L1-30</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -7381,37 +7793,37 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>L1-35-6.DTA</t>
+          <t>L1-30-1.DTA</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>54.2</v>
+        <v>0.6</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tue Jul 14 16:12:50 2020</t>
+          <t>Wed Jul 08 16:30:38 2020</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2020-07-15 10:34</t>
+          <t>2020-07-08 18:12</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2020-07-22 16:12</t>
+          <t>2020-07-16 16:30</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>距上一段 1.2 天（同一加载期内的停机夜歇）</t>
+          <t>首段</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>L1-35</t>
+          <t>L1-30</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -7426,37 +7838,37 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>L1-35-7.DTA</t>
+          <t>L1-30-2.DTA</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>185.5</v>
+        <v>0.2</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Wed Jul 15 11:21:20 2020</t>
+          <t>Thu Jul 09 12:10:56 2020</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2020-07-16 11:29</t>
+          <t>2020-07-09 12:27</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2020-07-23 11:21</t>
+          <t>2020-07-17 12:10</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>与上一段接续（间隔 19.1 小时）</t>
+          <t>与上一段接续（间隔 19.7 小时）</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>L1-35</t>
+          <t>L1-30</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -7466,42 +7878,28 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>AE 采集段</t>
+          <t>FBG 窗口</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>L1-35-8.DTA</t>
-        </is>
-      </c>
-      <c r="E44" t="n">
-        <v>85.09999999999999</v>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Thu Jul 16 11:52:23 2020</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>2020-07-16 17:02</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>2020-07-24 11:52</t>
-        </is>
-      </c>
+          <t>2020-07-16 → 2020-07-17（2 天）</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
-          <t>距上一段 1.0 天（同一加载期内的停机夜歇）</t>
+          <t>每 7 分钟 20 秒快照（全天覆盖，占空约 5%）；27 个分块</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>L1-35</t>
+          <t>L1-31</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -7511,28 +7909,42 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>FBG 窗口</t>
+          <t>AE 采集段</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2020-07-17 → 2020-07-25（9 天）</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
+          <t>L1-31-1.DTA</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>190.9</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Mon Jul 27 14:16:58 2020</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2020-08-01 03:11</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>2020-08-04 14:16</t>
+        </is>
+      </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>每 7 分钟 20 秒快照（全天覆盖，占空约 5%）；1779 个分块</t>
+          <t>首段</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>L1-36</t>
+          <t>L1-31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -7547,37 +7959,37 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>L1-36.DTA</t>
+          <t>L1-31-2.DTA</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>10.2</v>
+        <v>535.9</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Wed Jul 08 11:02:59 2020</t>
+          <t>Wed Aug 19 12:51:17 2020</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2020-07-08 11:45</t>
+          <t>2020-08-26 10:48</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2020-07-16 11:02</t>
+          <t>2020-08-27 12:51</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>首段</t>
+          <t>距上一段 23 天（推断为另一次加载）</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>L1-36</t>
+          <t>L1-31</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -7592,7 +8004,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2020-07-16 → 2020-07-16（1 天）</t>
+          <t>2020-08-04 → 2020-08-09（6 天）</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
@@ -7601,14 +8013,14 @@
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
-          <t>每 7 分钟 20 秒快照（全天覆盖，占空约 5%）；10 个分块</t>
+          <t>每 7 分钟 20 秒快照（全天覆盖，占空约 5%）；2420 个分块</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>L1-41</t>
+          <t>L1-31</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -7618,42 +8030,28 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>AE 采集段</t>
+          <t>FBG 窗口</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>L1-41.DTA</t>
-        </is>
-      </c>
-      <c r="E48" t="n">
-        <v>217</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Mon Oct 19 11:59:32 2020</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>2020-11-01 13:25</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>2020-10-27 11:59</t>
-        </is>
-      </c>
+          <t>2020-08-27 → 2020-09-03（8 天）</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
-          <t>首段</t>
+          <t>每 7 分钟 20 秒快照（全天覆盖，占空约 5%）；2420 个分块</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>L1-41</t>
+          <t>L1-34</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -7663,28 +8061,42 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>FBG 窗口</t>
+          <t>AE 采集段</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2020-10-26 → 2020-11-09（15 天）</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
+          <t>L1-34.DTA</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Wed Jul 08 14:20:59 2020</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2020-07-08 14:33</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>2020-07-16 14:20</t>
+        </is>
+      </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>每 7 分钟 20 秒快照（全天覆盖，占空约 5%）；2688 个分块</t>
+          <t>首段</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>L1-44</t>
+          <t>L1-34</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -7694,42 +8106,28 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>AE 采集段</t>
+          <t>FBG 窗口</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>L1-44-1.DTA</t>
-        </is>
-      </c>
-      <c r="E50" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Wed Oct 07 11:59:05 2020</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>2020-10-07 12:55</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>2020-10-15 11:59</t>
-        </is>
-      </c>
+          <t>2020-07-16 → 2020-07-16（1 天）</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
-          <t>首段</t>
+          <t>每 7 分钟 20 秒快照（全天覆盖，占空约 5%）；2 个分块</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>L1-44</t>
+          <t>L1-35</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -7744,37 +8142,37 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>L1-44-2.DTA</t>
+          <t>L1-35-1.DTA</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1906.4</v>
+        <v>61.9</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Wed Oct 07 12:59:43 2020</t>
+          <t>Thu Jul 09 15:19:43 2020</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2020-10-12 10:18</t>
+          <t>2020-07-10 12:20</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2020-10-15 12:59</t>
+          <t>2020-07-17 15:19</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>与上一段接续（间隔 1.0 小时）</t>
+          <t>首段</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>L1-44</t>
+          <t>L1-35</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -7789,37 +8187,37 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>L1-44-3.DTA</t>
+          <t>L1-35-2.DTA</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1549.1</v>
+        <v>115.6</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Wed Oct 07 12:59:43 2020</t>
+          <t>Fri Jul 10 12:21:07 2020</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2020-10-16 15:53</t>
+          <t>2020-07-11 11:30</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2020-10-15 12:59</t>
+          <t>2020-07-18 12:21</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>与上一卷同一采集启动时刻（DAQ 按卷续写，内容不重复）</t>
+          <t>与上一段接续（间隔 21.0 小时）</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>L1-44</t>
+          <t>L1-35</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -7829,33 +8227,47 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>FBG 窗口</t>
+          <t>AE 采集段</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2020-10-15 → 2020-10-24（10 天）</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
+          <t>L1-35-3.DTA</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Sat Jul 11 11:32:49 2020</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2020-07-11 19:41</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>2020-07-19 11:32</t>
+        </is>
+      </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>连续长记录；1849 个分块</t>
+          <t>与上一段接续（间隔 23.2 小时）</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>L1-49</t>
+          <t>L1-35</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>L1 恒幅+DFOS</t>
+          <t>L1 谱载+FBG</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -7865,34 +8277,42 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>L149.pridb</t>
+          <t>L1-35-4.DTA</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>285.6</v>
-      </c>
-      <c r="F54" t="inlineStr"/>
+        <v>158.8</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Sat Jul 11 19:50:24 2020</t>
+        </is>
+      </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2020-10-29 11:55</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr"/>
+          <t>2020-07-12 11:25</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>2020-07-19 19:50</t>
+        </is>
+      </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>首段</t>
+          <t>与上一段接续（间隔 8.3 小时）</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>L1-50</t>
+          <t>L1-35</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>L1 恒幅+DFOS</t>
+          <t>L1 谱载+FBG</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -7902,34 +8322,42 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>L150.pridb</t>
+          <t>L1-35-5.DTA</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>210.5</v>
-      </c>
-      <c r="F55" t="inlineStr"/>
+        <v>202.9</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Mon Jul 13 12:21:51 2020</t>
+        </is>
+      </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2020-11-05 19:27</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr"/>
+          <t>2020-07-14 16:00</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>2020-07-21 12:21</t>
+        </is>
+      </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>首段</t>
+          <t>距上一段 1.7 天（同一加载期内的停机夜歇）</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>L1-51</t>
+          <t>L1-35</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>L1 恒幅+DFOS</t>
+          <t>L1 谱载+FBG</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -7939,34 +8367,42 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>L151.pridb</t>
+          <t>L1-35-6.DTA</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>521.5</v>
-      </c>
-      <c r="F56" t="inlineStr"/>
+        <v>54.2</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Tue Jul 14 16:12:50 2020</t>
+        </is>
+      </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2020-10-26 12:58</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr"/>
+          <t>2020-07-15 10:34</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>2020-07-22 16:12</t>
+        </is>
+      </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>首段</t>
+          <t>距上一段 1.2 天（同一加载期内的停机夜歇）</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>L1-52</t>
+          <t>L1-35</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>L1 恒幅+DFOS</t>
+          <t>L1 谱载+FBG</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -7976,34 +8412,42 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>L152.pridb</t>
+          <t>L1-35-7.DTA</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1426</v>
-      </c>
-      <c r="F57" t="inlineStr"/>
+        <v>185.5</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Wed Jul 15 11:21:20 2020</t>
+        </is>
+      </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2020-10-02 10:14</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
+          <t>2020-07-16 11:29</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>2020-07-23 11:21</t>
+        </is>
+      </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>首段</t>
+          <t>与上一段接续（间隔 19.1 小时）</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>L1-54</t>
+          <t>L1-35</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>L1 恒幅+DFOS</t>
+          <t>L1 谱载+FBG</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -8013,71 +8457,73 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>L154.pridb</t>
+          <t>L1-35-8.DTA</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2196.1</v>
-      </c>
-      <c r="F58" t="inlineStr"/>
+        <v>85.09999999999999</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Thu Jul 16 11:52:23 2020</t>
+        </is>
+      </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2020-10-07 11:15</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr"/>
+          <t>2020-07-16 17:02</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>2020-07-24 11:52</t>
+        </is>
+      </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>首段</t>
+          <t>距上一段 1.0 天（同一加载期内的停机夜歇）</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>L1-55</t>
+          <t>L1-35</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>L1 恒幅+DFOS</t>
+          <t>L1 谱载+FBG</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>AE 采集段</t>
+          <t>FBG 窗口</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>L155.pridb</t>
-        </is>
-      </c>
-      <c r="E59" t="n">
-        <v>456.9</v>
-      </c>
+          <t>2020-07-17 → 2020-07-25（9 天）</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>2020-11-02 11:05</t>
-        </is>
-      </c>
+      <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
-          <t>首段</t>
+          <t>每 7 分钟 20 秒快照（全天覆盖，占空约 5%）；1779 个分块</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>L1-56</t>
+          <t>L1-36</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>L1 恒幅+DFOS</t>
+          <t>L1 谱载+FBG</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -8087,19 +8533,27 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>L156.pridb</t>
+          <t>L1-36.DTA</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2532</v>
-      </c>
-      <c r="F60" t="inlineStr"/>
+        <v>10.2</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Wed Jul 08 11:02:59 2020</t>
+        </is>
+      </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2020-10-16 10:52</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr"/>
+          <t>2020-07-08 11:45</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>2020-07-16 11:02</t>
+        </is>
+      </c>
       <c r="I60" t="inlineStr">
         <is>
           <t>首段</t>
@@ -8109,49 +8563,43 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>L1-59</t>
+          <t>L1-36</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>L1 恒幅+DFOS</t>
+          <t>L1 谱载+FBG</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>AE 采集段</t>
+          <t>FBG 窗口</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>L159-2.pridb</t>
-        </is>
-      </c>
-      <c r="E61" t="n">
-        <v>509.1</v>
-      </c>
+          <t>2020-07-16 → 2020-07-16（1 天）</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>2020-10-23 11:58</t>
-        </is>
-      </c>
+      <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
-          <t>首段</t>
+          <t>每 7 分钟 20 秒快照（全天覆盖，占空约 5%）；10 个分块</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>L1-59</t>
+          <t>L1-41</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>L1 恒幅+DFOS</t>
+          <t>L1 谱载+FBG</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -8161,57 +8609,595 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>L159.pridb</t>
+          <t>L1-41.DTA</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1</v>
-      </c>
-      <c r="F62" t="inlineStr"/>
+        <v>217</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Mon Oct 19 11:59:32 2020</t>
+        </is>
+      </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2020-10-20 14:51</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr"/>
+          <t>2020-11-01 13:25</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>2020-10-27 11:59</t>
+        </is>
+      </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>与上一卷同一采集启动时刻</t>
+          <t>首段</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>L1-60</t>
+          <t>L1-41</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>L1 恒幅+DFOS</t>
+          <t>L1 谱载+FBG</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>AE 采集段</t>
+          <t>FBG 窗口</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>L160.pridb</t>
-        </is>
-      </c>
-      <c r="E63" t="n">
-        <v>963.9</v>
-      </c>
+          <t>2020-10-26 → 2020-11-09（15 天）</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>2020-10-19 10:02</t>
-        </is>
-      </c>
+      <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
+        <is>
+          <t>每 7 分钟 20 秒快照（全天覆盖，占空约 5%）；2688 个分块</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>L1-44</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>L1 谱载+FBG</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>AE 采集段</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>L1-44-1.DTA</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Wed Oct 07 11:59:05 2020</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>2020-10-07 12:55</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>2020-10-15 11:59</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>首段</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>L1-44</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>L1 谱载+FBG</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>AE 采集段</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>L1-44-2.DTA</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>1906.4</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Wed Oct 07 12:59:43 2020</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>2020-10-12 10:18</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>2020-10-15 12:59</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>与上一段接续（间隔 1.0 小时）</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>L1-44</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>L1 谱载+FBG</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>AE 采集段</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>L1-44-3.DTA</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>1549.1</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Wed Oct 07 12:59:43 2020</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>2020-10-16 15:53</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>2020-10-15 12:59</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>与上一卷同一采集启动时刻（DAQ 按卷续写，内容不重复）</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>L1-44</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>L1 谱载+FBG</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>FBG 窗口</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2020-10-15 → 2020-10-24（10 天）</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>连续长记录；1849 个分块</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>L1-49</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>L1 恒幅+DFOS</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>AE 采集段</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>L149.pridb</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>285.6</v>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>2020-10-29 11:55</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>首段</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>L1-50</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>L1 恒幅+DFOS</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>AE 采集段</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>L150.pridb</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>210.5</v>
+      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>2020-11-05 19:27</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>首段</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>L1-51</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>L1 恒幅+DFOS</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>AE 采集段</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>L151.pridb</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>521.5</v>
+      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>2020-10-26 12:58</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>首段</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>L1-52</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>L1 恒幅+DFOS</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>AE 采集段</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>L152.pridb</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>1426</v>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>2020-10-02 10:14</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>首段</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>L1-54</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>L1 恒幅+DFOS</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>AE 采集段</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>L154.pridb</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>2196.1</v>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>2020-10-07 11:15</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>首段</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>L1-55</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>L1 恒幅+DFOS</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>AE 采集段</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>L155.pridb</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>456.9</v>
+      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>2020-11-02 11:05</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>首段</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>L1-56</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>L1 恒幅+DFOS</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>AE 采集段</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>L156.pridb</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>2532</v>
+      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>2020-10-16 10:52</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>首段</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>L1-59</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>L1 恒幅+DFOS</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>AE 采集段</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>L159-2.pridb</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>509.1</v>
+      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>2020-10-23 11:58</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>首段</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>L1-59</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>L1 恒幅+DFOS</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>AE 采集段</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>L159.pridb</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>1</v>
+      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>2020-10-20 14:51</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>与上一卷同一采集启动时刻</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>L1-60</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>L1 恒幅+DFOS</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>AE 采集段</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>L160.pridb</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>963.9</v>
+      </c>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>2020-10-19 10:02</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr">
         <is>
           <t>首段</t>
         </is>
@@ -8657,17 +9643,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>27 组全在 E:\l1；仓库 l1/ 已建好 27 个 junction（2026-10-04，`tools/relink_data.ps1 -Apply`）</t>
+          <t>29 组全在 E:\l1（数据本体只在外接盘，不入 D 盘仓库；2026-10-07 起不再用迁移脚本）</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>仓库内相对路径 l1/L1-xx/ 对全部 27 组都有效（以前只有 13 组）</t>
+          <t>仓库内相对路径 l1/L1-xx/ 对全部 29 组都有效（以前只有 13 组）</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>换盘只改 paths.json 的 data_root 再跑 -Apply；relink_data.ps1 的通配展开已改为「仓库侧 ∪ 数据盘侧」，盘上新增的组会自动补齐</t>
+          <t>换盘只改 paths.json 的 data_root 再跑 -Apply；数据侧新增的组在 paths.json 里补一条 item 即可被枚举到</t>
         </is>
       </c>
     </row>
@@ -8726,7 +9712,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M28"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9028,7 +10014,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>L1-24</t>
+          <t>L1-22</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -9044,10 +10030,10 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="n">
-        <v>1.075</v>
+        <v>0.999</v>
       </c>
       <c r="K9" t="n">
-        <v>62.5</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -9063,105 +10049,73 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>L1-25</t>
+          <t>L1-23</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>L1 谱载+FBG</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>3071</v>
-      </c>
-      <c r="D10" t="n">
-        <v>420</v>
-      </c>
-      <c r="E10" t="n">
-        <v>934.6</v>
-      </c>
-      <c r="F10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" t="n">
-        <v>576.6</v>
-      </c>
-      <c r="H10" t="n">
-        <v>100</v>
-      </c>
-      <c r="I10" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1.886</v>
-      </c>
-      <c r="K10" t="n">
-        <v>232.8</v>
-      </c>
+          <t>L1 恒幅+FBG+DFOS</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>小文件突发式（每文件 20 s 数据）</t>
+          <t>大文件（1 至 2 个连续长记录）</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>fill=holdgap</t>
+          <t>「文件间隔 / 空隙」概念不适用</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>L1-27</t>
+          <t>L1-24</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>L1 谱载+FBG</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>1020</v>
-      </c>
-      <c r="D11" t="n">
-        <v>420</v>
-      </c>
-      <c r="E11" t="n">
-        <v>120</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>99.2</v>
-      </c>
-      <c r="I11" t="n">
-        <v>5.7</v>
-      </c>
+          <t>L1 变幅VA+FBG</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="n">
-        <v>1.89</v>
+        <v>1.075</v>
       </c>
       <c r="K11" t="n">
-        <v>77.8</v>
+        <v>62.5</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>小文件突发式（每文件 20 s 数据）</t>
+          <t>大文件（1 至 2 个连续长记录）</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>fill=holdgap</t>
+          <t>「文件间隔 / 空隙」概念不适用</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>L1-29</t>
+          <t>L1-25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -9170,31 +10124,31 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3105</v>
+        <v>3071</v>
       </c>
       <c r="D12" t="n">
         <v>420</v>
       </c>
       <c r="E12" t="n">
-        <v>364.7</v>
+        <v>934.6</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>576.6</v>
       </c>
       <c r="H12" t="n">
-        <v>99.3</v>
+        <v>100</v>
       </c>
       <c r="I12" t="n">
-        <v>17.2</v>
+        <v>17.1</v>
       </c>
       <c r="J12" t="n">
-        <v>1.821</v>
+        <v>1.886</v>
       </c>
       <c r="K12" t="n">
-        <v>198.2</v>
+        <v>232.8</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -9210,7 +10164,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>L1-30</t>
+          <t>L1-27</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -9219,31 +10173,31 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>27</v>
+        <v>1020</v>
       </c>
       <c r="D13" t="n">
-        <v>240</v>
+        <v>420</v>
       </c>
       <c r="E13" t="n">
-        <v>19.7</v>
+        <v>120</v>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>18.1</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>105.1</v>
+        <v>99.2</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1</v>
+        <v>5.7</v>
       </c>
       <c r="J13" t="n">
-        <v>1.471</v>
+        <v>1.89</v>
       </c>
       <c r="K13" t="n">
-        <v>1.9</v>
+        <v>77.8</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -9252,14 +10206,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>fill=holdgap；文件数少，覆盖率估计不可靠</t>
+          <t>fill=holdgap</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>L1-31</t>
+          <t>L1-29</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -9268,31 +10222,31 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2420</v>
+        <v>3105</v>
       </c>
       <c r="D14" t="n">
         <v>420</v>
       </c>
       <c r="E14" t="n">
-        <v>716.2</v>
+        <v>364.7</v>
       </c>
       <c r="F14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>434.2</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>100</v>
+        <v>99.3</v>
       </c>
       <c r="I14" t="n">
-        <v>13.4</v>
+        <v>17.2</v>
       </c>
       <c r="J14" t="n">
-        <v>2.119</v>
+        <v>1.821</v>
       </c>
       <c r="K14" t="n">
-        <v>126.6</v>
+        <v>198.2</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -9308,7 +10262,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>L1-34</t>
+          <t>L1-30</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -9316,34 +10270,48 @@
           <t>L1 谱载+FBG</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
+      <c r="C15" t="n">
+        <v>27</v>
+      </c>
+      <c r="D15" t="n">
+        <v>240</v>
+      </c>
+      <c r="E15" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="H15" t="n">
+        <v>105.1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.1</v>
+      </c>
       <c r="J15" t="n">
-        <v>1.556</v>
+        <v>1.471</v>
       </c>
       <c r="K15" t="n">
-        <v>0.2</v>
+        <v>1.9</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>大文件（1 至 2 个连续长记录）</t>
+          <t>小文件突发式（每文件 20 s 数据）</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>「文件间隔 / 空隙」概念不适用</t>
+          <t>fill=holdgap；文件数少，覆盖率估计不可靠</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>L1-35</t>
+          <t>L1-31</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -9352,31 +10320,31 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1779</v>
+        <v>2420</v>
       </c>
       <c r="D16" t="n">
-        <v>240</v>
+        <v>420</v>
       </c>
       <c r="E16" t="n">
-        <v>187.5</v>
+        <v>716.2</v>
       </c>
       <c r="F16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G16" t="n">
-        <v>67.5</v>
+        <v>434.2</v>
       </c>
       <c r="H16" t="n">
-        <v>98.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="I16" t="n">
-        <v>9.9</v>
+        <v>13.4</v>
       </c>
       <c r="J16" t="n">
-        <v>1.872</v>
+        <v>2.119</v>
       </c>
       <c r="K16" t="n">
-        <v>67.09999999999999</v>
+        <v>126.6</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -9392,7 +10360,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>L1-36</t>
+          <t>L1-34</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -9400,48 +10368,34 @@
           <t>L1 谱载+FBG</t>
         </is>
       </c>
-      <c r="C17" t="n">
-        <v>10</v>
-      </c>
-      <c r="D17" t="n">
-        <v>240</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>111.1</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="n">
-        <v>1.667</v>
+        <v>1.556</v>
       </c>
       <c r="K17" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>小文件突发式（每文件 20 s 数据）</t>
+          <t>大文件（1 至 2 个连续长记录）</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>fill=holdgap；文件数少，覆盖率估计不可靠</t>
+          <t>「文件间隔 / 空隙」概念不适用</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>L1-41</t>
+          <t>L1-35</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -9450,31 +10404,31 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2688</v>
+        <v>1779</v>
       </c>
       <c r="D18" t="n">
-        <v>420</v>
+        <v>240</v>
       </c>
       <c r="E18" t="n">
-        <v>331.1</v>
+        <v>187.5</v>
       </c>
       <c r="F18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G18" t="n">
-        <v>17.8</v>
+        <v>67.5</v>
       </c>
       <c r="H18" t="n">
-        <v>100.1</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>14.9</v>
+        <v>9.9</v>
       </c>
       <c r="J18" t="n">
-        <v>1.857</v>
+        <v>1.872</v>
       </c>
       <c r="K18" t="n">
-        <v>272.2</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -9490,7 +10444,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>L1-44</t>
+          <t>L1-36</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -9499,31 +10453,31 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1849</v>
+        <v>10</v>
       </c>
       <c r="D19" t="n">
-        <v>420</v>
+        <v>240</v>
       </c>
       <c r="E19" t="n">
-        <v>220.2</v>
+        <v>0.6</v>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>99.59999999999999</v>
+        <v>111.1</v>
       </c>
       <c r="I19" t="n">
-        <v>10.3</v>
+        <v>0.1</v>
       </c>
       <c r="J19" t="n">
-        <v>1.891</v>
+        <v>1.667</v>
       </c>
       <c r="K19" t="n">
-        <v>170.4</v>
+        <v>0.8</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -9532,76 +10486,112 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>fill=holdgap</t>
+          <t>fill=holdgap；文件数少，覆盖率估计不可靠</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>L1-49</t>
+          <t>L1-41</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>L1 恒幅+DFOS</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+          <t>L1 谱载+FBG</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>2688</v>
+      </c>
+      <c r="D20" t="n">
+        <v>420</v>
+      </c>
+      <c r="E20" t="n">
+        <v>331.1</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="H20" t="n">
+        <v>100.1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.857</v>
+      </c>
+      <c r="K20" t="n">
+        <v>272.2</v>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>大文件（1 至 2 个连续长记录）</t>
+          <t>小文件突发式（每文件 20 s 数据）</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>「文件间隔 / 空隙」概念不适用</t>
+          <t>fill=holdgap</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>L1-50</t>
+          <t>L1-44</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>L1 恒幅+DFOS</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+          <t>L1 谱载+FBG</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1849</v>
+      </c>
+      <c r="D21" t="n">
+        <v>420</v>
+      </c>
+      <c r="E21" t="n">
+        <v>220.2</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H21" t="n">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="I21" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.891</v>
+      </c>
+      <c r="K21" t="n">
+        <v>170.4</v>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>大文件（1 至 2 个连续长记录）</t>
+          <t>小文件突发式（每文件 20 s 数据）</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>「文件间隔 / 空隙」概念不适用</t>
+          <t>fill=holdgap</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>L1-51</t>
+          <t>L1-49</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9632,7 +10622,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>L1-52</t>
+          <t>L1-50</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -9663,7 +10653,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>L1-54</t>
+          <t>L1-51</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -9694,7 +10684,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>L1-55</t>
+          <t>L1-52</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -9725,7 +10715,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>L1-56</t>
+          <t>L1-54</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -9756,7 +10746,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>L1-59</t>
+          <t>L1-55</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -9787,7 +10777,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>L1-60</t>
+          <t>L1-56</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -9810,6 +10800,68 @@
         </is>
       </c>
       <c r="M28" t="inlineStr">
+        <is>
+          <t>「文件间隔 / 空隙」概念不适用</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>L1-59</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>L1 恒幅+DFOS</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>大文件（1 至 2 个连续长记录）</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>「文件间隔 / 空隙」概念不适用</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>L1-60</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>L1 恒幅+DFOS</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>大文件（1 至 2 个连续长记录）</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
         <is>
           <t>「文件间隔 / 空隙」概念不适用</t>
         </is>
@@ -10242,7 +11294,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q27"/>
+  <dimension ref="A1:Q38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10518,53 +11570,53 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L1-24</t>
+          <t>L1-22</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>L1-24.DTA</t>
+          <t>L1-22_1.DTA</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>197.3</v>
+        <v>1906.4</v>
       </c>
       <c r="D5" t="n">
-        <v>4191234</v>
+        <v>945378</v>
       </c>
       <c r="E5" t="n">
-        <v>68.89</v>
+        <v>36.93</v>
       </c>
       <c r="F5" t="n">
-        <v>18.3</v>
+        <v>4.1</v>
       </c>
       <c r="G5" t="n">
-        <v>248005.3</v>
+        <v>132937.5</v>
       </c>
       <c r="H5" t="n">
-        <v>1137877</v>
+        <v>858146</v>
       </c>
       <c r="I5" t="n">
-        <v>3053357</v>
+        <v>87232</v>
       </c>
       <c r="J5" t="n">
         <v>60</v>
       </c>
       <c r="K5" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="L5" t="n">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="M5" t="n">
-        <v>42355</v>
+        <v>18465</v>
       </c>
       <c r="N5" t="n">
-        <v>368919</v>
+        <v>80113</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>2020-05-12 12:58:08</t>
+          <t>2020-05-07 10:09:56</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -10573,59 +11625,59 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>654</v>
+        <v>944695</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L1-25</t>
+          <t>L1-22</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>L1-25-1.DTA</t>
+          <t>L1-22_10.DTA</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>246</v>
+        <v>1906.4</v>
       </c>
       <c r="D6" t="n">
-        <v>4171534</v>
+        <v>949829</v>
       </c>
       <c r="E6" t="n">
-        <v>243.69</v>
+        <v>1.89</v>
       </c>
       <c r="F6" t="n">
-        <v>21.4</v>
+        <v>339050.2</v>
       </c>
       <c r="G6" t="n">
-        <v>877307</v>
+        <v>345850.2</v>
       </c>
       <c r="H6" t="n">
-        <v>2555015</v>
+        <v>798864</v>
       </c>
       <c r="I6" t="n">
-        <v>1616519</v>
+        <v>150965</v>
       </c>
       <c r="J6" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="K6" t="n">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="L6" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="M6" t="n">
-        <v>21899</v>
+        <v>440137</v>
       </c>
       <c r="N6" t="n">
-        <v>58102</v>
+        <v>485366</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>2020-08-26 12:04:11</t>
+          <t>2020-05-07 10:09:56</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -10634,59 +11686,59 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>949829</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L1-25</t>
+          <t>L1-22</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>L1-25-2.DTA</t>
+          <t>L1-22_11.DTA</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>174.6</v>
+        <v>698.5</v>
       </c>
       <c r="D7" t="n">
-        <v>3362718</v>
+        <v>348006</v>
       </c>
       <c r="E7" t="n">
-        <v>110.79</v>
+        <v>0.77</v>
       </c>
       <c r="F7" t="n">
-        <v>16.7</v>
+        <v>345850.2</v>
       </c>
       <c r="G7" t="n">
-        <v>398843.1</v>
+        <v>348637.7</v>
       </c>
       <c r="H7" t="n">
-        <v>2329792</v>
+        <v>277979</v>
       </c>
       <c r="I7" t="n">
-        <v>1032926</v>
+        <v>70027</v>
       </c>
       <c r="J7" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="K7" t="n">
         <v>64</v>
       </c>
       <c r="L7" t="n">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="M7" t="n">
-        <v>23388</v>
+        <v>348006</v>
       </c>
       <c r="N7" t="n">
-        <v>87248</v>
+        <v>348006</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>2020-09-29 16:07:27</t>
+          <t>2020-05-07 10:09:56</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -10695,43 +11747,43 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>348006</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>L1-27</t>
+          <t>L1-22</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>L1-27.DTA</t>
+          <t>L1-22_2.DTA</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1128.9</v>
+        <v>1906.4</v>
       </c>
       <c r="D8" t="n">
-        <v>26079969</v>
+        <v>947111</v>
       </c>
       <c r="E8" t="n">
-        <v>120.13</v>
+        <v>20.53</v>
       </c>
       <c r="F8" t="n">
-        <v>23.1</v>
+        <v>132937.7</v>
       </c>
       <c r="G8" t="n">
-        <v>432508.2</v>
+        <v>206857.9</v>
       </c>
       <c r="H8" t="n">
-        <v>2660196</v>
+        <v>798458</v>
       </c>
       <c r="I8" t="n">
-        <v>23419773</v>
+        <v>148653</v>
       </c>
       <c r="J8" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="K8" t="n">
         <v>67</v>
@@ -10740,14 +11792,14 @@
         <v>77</v>
       </c>
       <c r="M8" t="n">
-        <v>281116.5</v>
+        <v>45385</v>
       </c>
       <c r="N8" t="n">
-        <v>379624</v>
+        <v>58083</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>2020-07-17 11:19:05</t>
+          <t>2020-05-07 10:09:56</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -10756,59 +11808,59 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>947111</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>L1-29</t>
+          <t>L1-22</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>L1-29.DTA</t>
+          <t>L1-22_3.DTA</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>395.1</v>
+        <v>1906.4</v>
       </c>
       <c r="D9" t="n">
-        <v>7535512</v>
+        <v>948177</v>
       </c>
       <c r="E9" t="n">
-        <v>364.8</v>
+        <v>13.25</v>
       </c>
       <c r="F9" t="n">
-        <v>3.1</v>
+        <v>206858</v>
       </c>
       <c r="G9" t="n">
-        <v>1313273.2</v>
+        <v>254552.3</v>
       </c>
       <c r="H9" t="n">
-        <v>5343928</v>
+        <v>798603</v>
       </c>
       <c r="I9" t="n">
-        <v>2191584</v>
+        <v>149574</v>
       </c>
       <c r="J9" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="K9" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="L9" t="n">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="M9" t="n">
-        <v>22635.5</v>
+        <v>68443</v>
       </c>
       <c r="N9" t="n">
-        <v>113670</v>
+        <v>82616</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>2020-09-13 11:48:18</t>
+          <t>2020-05-07 10:09:56</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -10817,59 +11869,59 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>948177</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>L1-30</t>
+          <t>L1-22</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>L1-30-1.DTA</t>
+          <t>L1-22_4.DTA</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.6</v>
+        <v>1906.4</v>
       </c>
       <c r="D10" t="n">
-        <v>2239</v>
+        <v>949094</v>
       </c>
       <c r="E10" t="n">
-        <v>1.68</v>
+        <v>6.89</v>
       </c>
       <c r="F10" t="n">
-        <v>17.2</v>
+        <v>254552.5</v>
       </c>
       <c r="G10" t="n">
-        <v>6058</v>
+        <v>279354.8</v>
       </c>
       <c r="H10" t="n">
-        <v>1135</v>
+        <v>865199</v>
       </c>
       <c r="I10" t="n">
-        <v>1104</v>
+        <v>83895</v>
       </c>
       <c r="J10" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="K10" t="n">
-        <v>91</v>
+        <v>66</v>
       </c>
       <c r="L10" t="n">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="M10" t="n">
-        <v>1119.5</v>
+        <v>117677</v>
       </c>
       <c r="N10" t="n">
-        <v>2212</v>
+        <v>175072</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2020-07-08 16:30:38</t>
+          <t>2020-05-07 10:09:56</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -10878,59 +11930,59 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>949094</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>L1-30</t>
+          <t>L1-22</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>L1-30-2.DTA</t>
+          <t>L1-22_5.DTA</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.2</v>
+        <v>1906.5</v>
       </c>
       <c r="D11" t="n">
-        <v>1717</v>
+        <v>949447</v>
       </c>
       <c r="E11" t="n">
-        <v>0.21</v>
+        <v>4.73</v>
       </c>
       <c r="F11" t="n">
-        <v>21.3</v>
+        <v>279354.8</v>
       </c>
       <c r="G11" t="n">
-        <v>791.7</v>
+        <v>296391.4</v>
       </c>
       <c r="H11" t="n">
-        <v>832</v>
+        <v>895278</v>
       </c>
       <c r="I11" t="n">
-        <v>885</v>
+        <v>54169</v>
       </c>
       <c r="J11" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="K11" t="n">
+        <v>63</v>
+      </c>
+      <c r="L11" t="n">
         <v>70</v>
       </c>
-      <c r="L11" t="n">
-        <v>94</v>
-      </c>
       <c r="M11" t="n">
-        <v>1717</v>
+        <v>179225.5</v>
       </c>
       <c r="N11" t="n">
-        <v>1717</v>
+        <v>216749</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2020-07-09 12:10:56</t>
+          <t>2020-05-07 10:09:56</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -10939,59 +11991,59 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>949447</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>L1-31</t>
+          <t>L1-22</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>L1-31-1.DTA</t>
+          <t>L1-22_6.DTA</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>190.9</v>
+        <v>1906.4</v>
       </c>
       <c r="D12" t="n">
-        <v>3794911</v>
+        <v>949617</v>
       </c>
       <c r="E12" t="n">
-        <v>108.9</v>
+        <v>3.31</v>
       </c>
       <c r="F12" t="n">
-        <v>18.4</v>
+        <v>296391.4</v>
       </c>
       <c r="G12" t="n">
-        <v>392073.8</v>
+        <v>308302.7</v>
       </c>
       <c r="H12" t="n">
-        <v>2821014</v>
+        <v>844527</v>
       </c>
       <c r="I12" t="n">
-        <v>973897</v>
+        <v>105090</v>
       </c>
       <c r="J12" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="K12" t="n">
         <v>63</v>
       </c>
       <c r="L12" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="M12" t="n">
-        <v>43207</v>
+        <v>224923</v>
       </c>
       <c r="N12" t="n">
-        <v>99057</v>
+        <v>330388</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2020-07-27 14:16:58</t>
+          <t>2020-05-07 10:09:56</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -11000,59 +12052,59 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>949617</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>L1-31</t>
+          <t>L1-22</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>L1-31-2.DTA</t>
+          <t>L1-22_7.DTA</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>535.9</v>
+        <v>1906.4</v>
       </c>
       <c r="D13" t="n">
-        <v>11625150</v>
+        <v>949601</v>
       </c>
       <c r="E13" t="n">
-        <v>165.81</v>
+        <v>3.41</v>
       </c>
       <c r="F13" t="n">
-        <v>35</v>
+        <v>308302.9</v>
       </c>
       <c r="G13" t="n">
-        <v>596967.3</v>
+        <v>320580.4</v>
       </c>
       <c r="H13" t="n">
-        <v>10546441</v>
+        <v>864958</v>
       </c>
       <c r="I13" t="n">
-        <v>1078709</v>
+        <v>84643</v>
       </c>
       <c r="J13" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="K13" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="L13" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="M13" t="n">
-        <v>121605.5</v>
+        <v>261939</v>
       </c>
       <c r="N13" t="n">
-        <v>203559</v>
+        <v>276128</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2020-08-19 12:51:17</t>
+          <t>2020-05-07 10:09:56</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -11061,59 +12113,59 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>949601</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>L1-34</t>
+          <t>L1-22</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>L1-34.DTA</t>
+          <t>L1-22_8.DTA</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1.5</v>
+        <v>1906.5</v>
       </c>
       <c r="D14" t="n">
-        <v>33361</v>
+        <v>949717</v>
       </c>
       <c r="E14" t="n">
-        <v>0.19</v>
+        <v>2.79</v>
       </c>
       <c r="F14" t="n">
-        <v>36.6</v>
+        <v>320580.4</v>
       </c>
       <c r="G14" t="n">
-        <v>722.9</v>
+        <v>330622.3</v>
       </c>
       <c r="H14" t="n">
-        <v>7097</v>
+        <v>849513</v>
       </c>
       <c r="I14" t="n">
-        <v>26264</v>
+        <v>100204</v>
       </c>
       <c r="J14" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="K14" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="L14" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M14" t="n">
-        <v>33361</v>
+        <v>303485</v>
       </c>
       <c r="N14" t="n">
-        <v>33361</v>
+        <v>365449</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>2020-07-08 14:20:59</t>
+          <t>2020-05-07 10:09:56</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -11122,59 +12174,59 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>949717</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>L1-35</t>
+          <t>L1-22</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>L1-35-1.DTA</t>
+          <t>L1-22_9.DTA</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>61.9</v>
+        <v>1906.4</v>
       </c>
       <c r="D15" t="n">
-        <v>1334254</v>
+        <v>949760</v>
       </c>
       <c r="E15" t="n">
-        <v>20.68</v>
+        <v>2.34</v>
       </c>
       <c r="F15" t="n">
-        <v>19</v>
+        <v>330622.5</v>
       </c>
       <c r="G15" t="n">
-        <v>74474.89999999999</v>
+        <v>339050.2</v>
       </c>
       <c r="H15" t="n">
-        <v>1309877</v>
+        <v>814687</v>
       </c>
       <c r="I15" t="n">
-        <v>24377</v>
+        <v>135073</v>
       </c>
       <c r="J15" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="K15" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="L15" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="M15" t="n">
-        <v>604.5</v>
+        <v>230250</v>
       </c>
       <c r="N15" t="n">
-        <v>312953</v>
+        <v>418594</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>2020-07-09 15:19:43</t>
+          <t>2020-05-07 10:09:56</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -11183,59 +12235,59 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>949760</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>L1-35</t>
+          <t>L1-24</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>L1-35-2.DTA</t>
+          <t>L1-24.DTA</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>115.6</v>
+        <v>197.3</v>
       </c>
       <c r="D16" t="n">
-        <v>2592079</v>
+        <v>4191234</v>
       </c>
       <c r="E16" t="n">
-        <v>23.15</v>
+        <v>68.89</v>
       </c>
       <c r="F16" t="n">
-        <v>20.7</v>
+        <v>18.3</v>
       </c>
       <c r="G16" t="n">
-        <v>83365.2</v>
+        <v>248005.3</v>
       </c>
       <c r="H16" t="n">
-        <v>2524602</v>
+        <v>1137877</v>
       </c>
       <c r="I16" t="n">
-        <v>67477</v>
+        <v>3053357</v>
       </c>
       <c r="J16" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="K16" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="L16" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="M16" t="n">
-        <v>129872</v>
+        <v>42355</v>
       </c>
       <c r="N16" t="n">
-        <v>254083</v>
+        <v>368919</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>2020-07-10 12:21:07</t>
+          <t>2020-05-12 12:58:08</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -11244,59 +12296,59 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>654</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>L1-35</t>
+          <t>L1-25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>L1-35-3.DTA</t>
+          <t>L1-25-1.DTA</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>37.3</v>
+        <v>246</v>
       </c>
       <c r="D17" t="n">
-        <v>832136</v>
+        <v>4171534</v>
       </c>
       <c r="E17" t="n">
-        <v>7.93</v>
+        <v>243.69</v>
       </c>
       <c r="F17" t="n">
-        <v>601</v>
+        <v>21.4</v>
       </c>
       <c r="G17" t="n">
-        <v>29146.8</v>
+        <v>877307</v>
       </c>
       <c r="H17" t="n">
-        <v>822682</v>
+        <v>2555015</v>
       </c>
       <c r="I17" t="n">
-        <v>9454</v>
+        <v>1616519</v>
       </c>
       <c r="J17" t="n">
         <v>62</v>
       </c>
       <c r="K17" t="n">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="L17" t="n">
-        <v>71</v>
+        <v>91</v>
       </c>
       <c r="M17" t="n">
-        <v>187000</v>
+        <v>21899</v>
       </c>
       <c r="N17" t="n">
-        <v>240188</v>
+        <v>58102</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>2020-07-11 11:32:49</t>
+          <t>2020-08-26 12:04:11</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -11311,53 +12363,53 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>L1-35</t>
+          <t>L1-25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>L1-35-4.DTA</t>
+          <t>L1-25-2.DTA</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>158.8</v>
+        <v>174.6</v>
       </c>
       <c r="D18" t="n">
-        <v>3674942</v>
+        <v>3362718</v>
       </c>
       <c r="E18" t="n">
-        <v>15.54</v>
+        <v>110.79</v>
       </c>
       <c r="F18" t="n">
-        <v>17.3</v>
+        <v>16.7</v>
       </c>
       <c r="G18" t="n">
-        <v>55957.5</v>
+        <v>398843.1</v>
       </c>
       <c r="H18" t="n">
-        <v>3594402</v>
+        <v>2329792</v>
       </c>
       <c r="I18" t="n">
-        <v>80540</v>
+        <v>1032926</v>
       </c>
       <c r="J18" t="n">
         <v>62</v>
       </c>
       <c r="K18" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="L18" t="n">
         <v>70</v>
       </c>
       <c r="M18" t="n">
-        <v>232550.5</v>
+        <v>23388</v>
       </c>
       <c r="N18" t="n">
-        <v>265551</v>
+        <v>87248</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>2020-07-11 19:50:24</t>
+          <t>2020-09-29 16:07:27</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -11372,53 +12424,53 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>L1-35</t>
+          <t>L1-27</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>L1-35-5.DTA</t>
+          <t>L1-27.DTA</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>202.9</v>
+        <v>1128.9</v>
       </c>
       <c r="D19" t="n">
-        <v>4643380</v>
+        <v>26079969</v>
       </c>
       <c r="E19" t="n">
-        <v>27.6</v>
+        <v>120.13</v>
       </c>
       <c r="F19" t="n">
-        <v>18.5</v>
+        <v>23.1</v>
       </c>
       <c r="G19" t="n">
-        <v>99364.10000000001</v>
+        <v>432508.2</v>
       </c>
       <c r="H19" t="n">
-        <v>4400068</v>
+        <v>2660196</v>
       </c>
       <c r="I19" t="n">
-        <v>243312</v>
+        <v>23419773</v>
       </c>
       <c r="J19" t="n">
         <v>62</v>
       </c>
       <c r="K19" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="L19" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="M19" t="n">
-        <v>214120</v>
+        <v>281116.5</v>
       </c>
       <c r="N19" t="n">
-        <v>344867</v>
+        <v>379624</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>2020-07-13 12:21:51</t>
+          <t>2020-07-17 11:19:05</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -11433,53 +12485,53 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>L1-35</t>
+          <t>L1-29</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>L1-35-6.DTA</t>
+          <t>L1-29.DTA</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>54.2</v>
+        <v>395.1</v>
       </c>
       <c r="D20" t="n">
-        <v>1163464</v>
+        <v>7535512</v>
       </c>
       <c r="E20" t="n">
-        <v>18.35</v>
+        <v>364.8</v>
       </c>
       <c r="F20" t="n">
-        <v>21.2</v>
+        <v>3.1</v>
       </c>
       <c r="G20" t="n">
-        <v>66093.7</v>
+        <v>1313273.2</v>
       </c>
       <c r="H20" t="n">
-        <v>989515</v>
+        <v>5343928</v>
       </c>
       <c r="I20" t="n">
-        <v>173949</v>
+        <v>2191584</v>
       </c>
       <c r="J20" t="n">
         <v>62</v>
       </c>
       <c r="K20" t="n">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="L20" t="n">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="M20" t="n">
-        <v>18.5</v>
+        <v>22635.5</v>
       </c>
       <c r="N20" t="n">
-        <v>241353</v>
+        <v>113670</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2020-07-14 16:12:50</t>
+          <t>2020-09-13 11:48:18</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -11494,53 +12546,53 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>L1-35</t>
+          <t>L1-30</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>L1-35-7.DTA</t>
+          <t>L1-30-1.DTA</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>185.5</v>
+        <v>0.6</v>
       </c>
       <c r="D21" t="n">
-        <v>4253057</v>
+        <v>2239</v>
       </c>
       <c r="E21" t="n">
-        <v>23.89</v>
+        <v>1.68</v>
       </c>
       <c r="F21" t="n">
-        <v>15</v>
+        <v>17.2</v>
       </c>
       <c r="G21" t="n">
-        <v>86027.60000000001</v>
+        <v>6058</v>
       </c>
       <c r="H21" t="n">
-        <v>3349132</v>
+        <v>1135</v>
       </c>
       <c r="I21" t="n">
-        <v>903925</v>
+        <v>1104</v>
       </c>
       <c r="J21" t="n">
         <v>62</v>
       </c>
       <c r="K21" t="n">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="L21" t="n">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="M21" t="n">
-        <v>292277</v>
+        <v>1119.5</v>
       </c>
       <c r="N21" t="n">
-        <v>394586</v>
+        <v>2212</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>2020-07-15 11:21:20</t>
+          <t>2020-07-08 16:30:38</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -11555,53 +12607,53 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>L1-35</t>
+          <t>L1-30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>L1-35-8.DTA</t>
+          <t>L1-30-2.DTA</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>85.09999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="D22" t="n">
-        <v>1990951</v>
+        <v>1717</v>
       </c>
       <c r="E22" t="n">
-        <v>4.53</v>
+        <v>0.21</v>
       </c>
       <c r="F22" t="n">
-        <v>17.4</v>
+        <v>21.3</v>
       </c>
       <c r="G22" t="n">
-        <v>16320.4</v>
+        <v>791.7</v>
       </c>
       <c r="H22" t="n">
-        <v>1402607</v>
+        <v>832</v>
       </c>
       <c r="I22" t="n">
-        <v>588344</v>
+        <v>885</v>
       </c>
       <c r="J22" t="n">
         <v>62</v>
       </c>
       <c r="K22" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L22" t="n">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="M22" t="n">
-        <v>473680</v>
+        <v>1717</v>
       </c>
       <c r="N22" t="n">
-        <v>481448</v>
+        <v>1717</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>2020-07-16 11:52:23</t>
+          <t>2020-07-09 12:10:56</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -11616,53 +12668,53 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>L1-36</t>
+          <t>L1-31</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>L1-36.DTA</t>
+          <t>L1-31-1.DTA</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>10.2</v>
+        <v>190.9</v>
       </c>
       <c r="D23" t="n">
-        <v>238575</v>
+        <v>3794911</v>
       </c>
       <c r="E23" t="n">
-        <v>0.7</v>
+        <v>108.9</v>
       </c>
       <c r="F23" t="n">
-        <v>13.1</v>
+        <v>18.4</v>
       </c>
       <c r="G23" t="n">
-        <v>2534.3</v>
+        <v>392073.8</v>
       </c>
       <c r="H23" t="n">
-        <v>193690</v>
+        <v>2821014</v>
       </c>
       <c r="I23" t="n">
-        <v>44885</v>
+        <v>973897</v>
       </c>
       <c r="J23" t="n">
         <v>62</v>
       </c>
       <c r="K23" t="n">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="L23" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="M23" t="n">
-        <v>238575</v>
+        <v>43207</v>
       </c>
       <c r="N23" t="n">
-        <v>238575</v>
+        <v>99057</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>2020-07-08 11:02:59</t>
+          <t>2020-07-27 14:16:58</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -11677,53 +12729,53 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>L1-41</t>
+          <t>L1-31</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>L1-41.DTA</t>
+          <t>L1-31-2.DTA</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>217</v>
+        <v>535.9</v>
       </c>
       <c r="D24" t="n">
-        <v>2996566</v>
+        <v>11625150</v>
       </c>
       <c r="E24" t="n">
-        <v>313.42</v>
+        <v>165.81</v>
       </c>
       <c r="F24" t="n">
-        <v>39.5</v>
+        <v>35</v>
       </c>
       <c r="G24" t="n">
-        <v>1128364.8</v>
+        <v>596967.3</v>
       </c>
       <c r="H24" t="n">
-        <v>1599895</v>
+        <v>10546441</v>
       </c>
       <c r="I24" t="n">
-        <v>1396671</v>
+        <v>1078709</v>
       </c>
       <c r="J24" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="K24" t="n">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="L24" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="M24" t="n">
-        <v>5627</v>
+        <v>121605.5</v>
       </c>
       <c r="N24" t="n">
-        <v>214996</v>
+        <v>203559</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2020-10-19 11:59:32</t>
+          <t>2020-08-19 12:51:17</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -11738,53 +12790,53 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>L1-44</t>
+          <t>L1-34</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>L1-44-1.DTA</t>
+          <t>L1-34.DTA</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="D25" t="n">
-        <v>12479</v>
+        <v>33361</v>
       </c>
       <c r="E25" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="F25" t="n">
-        <v>22</v>
+        <v>36.6</v>
       </c>
       <c r="G25" t="n">
-        <v>739.7</v>
+        <v>722.9</v>
       </c>
       <c r="H25" t="n">
-        <v>6589</v>
+        <v>7097</v>
       </c>
       <c r="I25" t="n">
-        <v>5890</v>
+        <v>26264</v>
       </c>
       <c r="J25" t="n">
         <v>62</v>
       </c>
       <c r="K25" t="n">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="L25" t="n">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="M25" t="n">
-        <v>12479</v>
+        <v>33361</v>
       </c>
       <c r="N25" t="n">
-        <v>12479</v>
+        <v>33361</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>2020-10-07 11:59:05</t>
+          <t>2020-07-08 14:20:59</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -11799,53 +12851,53 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>L1-44</t>
+          <t>L1-35</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>L1-44-2.DTA</t>
+          <t>L1-35-1.DTA</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1906.4</v>
+        <v>61.9</v>
       </c>
       <c r="D26" t="n">
-        <v>44615237</v>
+        <v>1334254</v>
       </c>
       <c r="E26" t="n">
-        <v>117.3</v>
+        <v>20.68</v>
       </c>
       <c r="F26" t="n">
-        <v>21.5</v>
+        <v>19</v>
       </c>
       <c r="G26" t="n">
-        <v>422314.2</v>
+        <v>74474.89999999999</v>
       </c>
       <c r="H26" t="n">
-        <v>42705875</v>
+        <v>1309877</v>
       </c>
       <c r="I26" t="n">
-        <v>1909362</v>
+        <v>24377</v>
       </c>
       <c r="J26" t="n">
         <v>62</v>
       </c>
       <c r="K26" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="L26" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="M26" t="n">
-        <v>424997.5</v>
+        <v>604.5</v>
       </c>
       <c r="N26" t="n">
-        <v>484182</v>
+        <v>312953</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>2020-10-07 12:59:43</t>
+          <t>2020-07-09 15:19:43</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -11860,61 +12912,732 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>L1-44</t>
+          <t>L1-35</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>L1-44-3.DTA</t>
+          <t>L1-35-2.DTA</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1549.1</v>
+        <v>115.6</v>
       </c>
       <c r="D27" t="n">
-        <v>36211634</v>
+        <v>2592079</v>
       </c>
       <c r="E27" t="n">
-        <v>81.31999999999999</v>
+        <v>23.15</v>
       </c>
       <c r="F27" t="n">
-        <v>422314.2</v>
+        <v>20.7</v>
       </c>
       <c r="G27" t="n">
-        <v>715074.3</v>
+        <v>83365.2</v>
       </c>
       <c r="H27" t="n">
-        <v>32999882</v>
+        <v>2524602</v>
       </c>
       <c r="I27" t="n">
-        <v>3211752</v>
+        <v>67477</v>
       </c>
       <c r="J27" t="n">
         <v>62</v>
       </c>
       <c r="K27" t="n">
+        <v>66</v>
+      </c>
+      <c r="L27" t="n">
+        <v>73</v>
+      </c>
+      <c r="M27" t="n">
+        <v>129872</v>
+      </c>
+      <c r="N27" t="n">
+        <v>254083</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>2020-07-10 12:21:07</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>1000/1000</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>L1-35</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>L1-35-3.DTA</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="D28" t="n">
+        <v>832136</v>
+      </c>
+      <c r="E28" t="n">
+        <v>7.93</v>
+      </c>
+      <c r="F28" t="n">
+        <v>601</v>
+      </c>
+      <c r="G28" t="n">
+        <v>29146.8</v>
+      </c>
+      <c r="H28" t="n">
+        <v>822682</v>
+      </c>
+      <c r="I28" t="n">
+        <v>9454</v>
+      </c>
+      <c r="J28" t="n">
+        <v>62</v>
+      </c>
+      <c r="K28" t="n">
+        <v>65</v>
+      </c>
+      <c r="L28" t="n">
+        <v>71</v>
+      </c>
+      <c r="M28" t="n">
+        <v>187000</v>
+      </c>
+      <c r="N28" t="n">
+        <v>240188</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>2020-07-11 11:32:49</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>1000/1000</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>L1-35</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>L1-35-4.DTA</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>158.8</v>
+      </c>
+      <c r="D29" t="n">
+        <v>3674942</v>
+      </c>
+      <c r="E29" t="n">
+        <v>15.54</v>
+      </c>
+      <c r="F29" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="G29" t="n">
+        <v>55957.5</v>
+      </c>
+      <c r="H29" t="n">
+        <v>3594402</v>
+      </c>
+      <c r="I29" t="n">
+        <v>80540</v>
+      </c>
+      <c r="J29" t="n">
+        <v>62</v>
+      </c>
+      <c r="K29" t="n">
+        <v>66</v>
+      </c>
+      <c r="L29" t="n">
+        <v>70</v>
+      </c>
+      <c r="M29" t="n">
+        <v>232550.5</v>
+      </c>
+      <c r="N29" t="n">
+        <v>265551</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>2020-07-11 19:50:24</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>1000/1000</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>L1-35</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>L1-35-5.DTA</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>202.9</v>
+      </c>
+      <c r="D30" t="n">
+        <v>4643380</v>
+      </c>
+      <c r="E30" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="F30" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="G30" t="n">
+        <v>99364.10000000001</v>
+      </c>
+      <c r="H30" t="n">
+        <v>4400068</v>
+      </c>
+      <c r="I30" t="n">
+        <v>243312</v>
+      </c>
+      <c r="J30" t="n">
+        <v>62</v>
+      </c>
+      <c r="K30" t="n">
+        <v>66</v>
+      </c>
+      <c r="L30" t="n">
+        <v>73</v>
+      </c>
+      <c r="M30" t="n">
+        <v>214120</v>
+      </c>
+      <c r="N30" t="n">
+        <v>344867</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>2020-07-13 12:21:51</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>1000/1000</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>L1-35</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>L1-35-6.DTA</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1163464</v>
+      </c>
+      <c r="E31" t="n">
+        <v>18.35</v>
+      </c>
+      <c r="F31" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="G31" t="n">
+        <v>66093.7</v>
+      </c>
+      <c r="H31" t="n">
+        <v>989515</v>
+      </c>
+      <c r="I31" t="n">
+        <v>173949</v>
+      </c>
+      <c r="J31" t="n">
+        <v>62</v>
+      </c>
+      <c r="K31" t="n">
+        <v>67</v>
+      </c>
+      <c r="L31" t="n">
+        <v>75</v>
+      </c>
+      <c r="M31" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="N31" t="n">
+        <v>241353</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>2020-07-14 16:12:50</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>1000/1000</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>L1-35</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>L1-35-7.DTA</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>185.5</v>
+      </c>
+      <c r="D32" t="n">
+        <v>4253057</v>
+      </c>
+      <c r="E32" t="n">
+        <v>23.89</v>
+      </c>
+      <c r="F32" t="n">
+        <v>15</v>
+      </c>
+      <c r="G32" t="n">
+        <v>86027.60000000001</v>
+      </c>
+      <c r="H32" t="n">
+        <v>3349132</v>
+      </c>
+      <c r="I32" t="n">
+        <v>903925</v>
+      </c>
+      <c r="J32" t="n">
+        <v>62</v>
+      </c>
+      <c r="K32" t="n">
+        <v>69</v>
+      </c>
+      <c r="L32" t="n">
+        <v>82</v>
+      </c>
+      <c r="M32" t="n">
+        <v>292277</v>
+      </c>
+      <c r="N32" t="n">
+        <v>394586</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>2020-07-15 11:21:20</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>1000/1000</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>L1-35</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>L1-35-8.DTA</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>85.09999999999999</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1990951</v>
+      </c>
+      <c r="E33" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="F33" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="G33" t="n">
+        <v>16320.4</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1402607</v>
+      </c>
+      <c r="I33" t="n">
+        <v>588344</v>
+      </c>
+      <c r="J33" t="n">
+        <v>62</v>
+      </c>
+      <c r="K33" t="n">
+        <v>69</v>
+      </c>
+      <c r="L33" t="n">
+        <v>78</v>
+      </c>
+      <c r="M33" t="n">
+        <v>473680</v>
+      </c>
+      <c r="N33" t="n">
+        <v>481448</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>2020-07-16 11:52:23</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>1000/1000</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>L1-36</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>L1-36.DTA</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="D34" t="n">
+        <v>238575</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F34" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="G34" t="n">
+        <v>2534.3</v>
+      </c>
+      <c r="H34" t="n">
+        <v>193690</v>
+      </c>
+      <c r="I34" t="n">
+        <v>44885</v>
+      </c>
+      <c r="J34" t="n">
+        <v>62</v>
+      </c>
+      <c r="K34" t="n">
+        <v>67</v>
+      </c>
+      <c r="L34" t="n">
+        <v>79</v>
+      </c>
+      <c r="M34" t="n">
+        <v>238575</v>
+      </c>
+      <c r="N34" t="n">
+        <v>238575</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>2020-07-08 11:02:59</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>1000/1000</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>L1-41</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>L1-41.DTA</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>217</v>
+      </c>
+      <c r="D35" t="n">
+        <v>2996566</v>
+      </c>
+      <c r="E35" t="n">
+        <v>313.42</v>
+      </c>
+      <c r="F35" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="G35" t="n">
+        <v>1128364.8</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1599895</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1396671</v>
+      </c>
+      <c r="J35" t="n">
+        <v>65</v>
+      </c>
+      <c r="K35" t="n">
+        <v>77</v>
+      </c>
+      <c r="L35" t="n">
+        <v>91</v>
+      </c>
+      <c r="M35" t="n">
+        <v>5627</v>
+      </c>
+      <c r="N35" t="n">
+        <v>214996</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>2020-10-19 11:59:32</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>1000/1000</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>L1-44</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>L1-44-1.DTA</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D36" t="n">
+        <v>12479</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F36" t="n">
+        <v>22</v>
+      </c>
+      <c r="G36" t="n">
+        <v>739.7</v>
+      </c>
+      <c r="H36" t="n">
+        <v>6589</v>
+      </c>
+      <c r="I36" t="n">
+        <v>5890</v>
+      </c>
+      <c r="J36" t="n">
+        <v>62</v>
+      </c>
+      <c r="K36" t="n">
+        <v>83</v>
+      </c>
+      <c r="L36" t="n">
+        <v>95</v>
+      </c>
+      <c r="M36" t="n">
+        <v>12479</v>
+      </c>
+      <c r="N36" t="n">
+        <v>12479</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>2020-10-07 11:59:05</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>1000/1000</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>L1-44</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>L1-44-2.DTA</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>1906.4</v>
+      </c>
+      <c r="D37" t="n">
+        <v>44615237</v>
+      </c>
+      <c r="E37" t="n">
+        <v>117.3</v>
+      </c>
+      <c r="F37" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="G37" t="n">
+        <v>422314.2</v>
+      </c>
+      <c r="H37" t="n">
+        <v>42705875</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1909362</v>
+      </c>
+      <c r="J37" t="n">
+        <v>62</v>
+      </c>
+      <c r="K37" t="n">
+        <v>63</v>
+      </c>
+      <c r="L37" t="n">
+        <v>79</v>
+      </c>
+      <c r="M37" t="n">
+        <v>424997.5</v>
+      </c>
+      <c r="N37" t="n">
+        <v>484182</v>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>2020-10-07 12:59:43</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>1000/1000</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>L1-44</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>L1-44-3.DTA</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>1549.1</v>
+      </c>
+      <c r="D38" t="n">
+        <v>36211634</v>
+      </c>
+      <c r="E38" t="n">
+        <v>81.31999999999999</v>
+      </c>
+      <c r="F38" t="n">
+        <v>422314.2</v>
+      </c>
+      <c r="G38" t="n">
+        <v>715074.3</v>
+      </c>
+      <c r="H38" t="n">
+        <v>32999882</v>
+      </c>
+      <c r="I38" t="n">
+        <v>3211752</v>
+      </c>
+      <c r="J38" t="n">
+        <v>62</v>
+      </c>
+      <c r="K38" t="n">
         <v>64</v>
       </c>
-      <c r="L27" t="n">
+      <c r="L38" t="n">
         <v>68</v>
       </c>
-      <c r="M27" t="n">
+      <c r="M38" t="n">
         <v>437411.5</v>
       </c>
-      <c r="N27" t="n">
+      <c r="N38" t="n">
         <v>601649</v>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="O38" t="inlineStr">
         <is>
           <t>2020-10-07 12:59:43</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="P38" t="inlineStr">
         <is>
           <t>1000/1000</t>
         </is>
       </c>
-      <c r="Q27" t="n">
+      <c r="Q38" t="n">
         <v>0</v>
       </c>
     </row>

--- a/l1/L1数据记录.xlsx
+++ b/l1/L1数据记录.xlsx
@@ -9599,17 +9599,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>变幅表里的 L1-22 未提供；一批表里的 L1-23 未提供</t>
+          <t>无 —— L1-22（变幅表）与 L1-23（一批表）已于 2026-10-09 由数据方补齐并接入</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>变幅组实际 4/5 组，一批 4/5 组</t>
+          <t>四个分组现在都是满员：C1 5 组 / C2 9 组 / C3 5 组 / C4 10 组 = 29 组</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>如需完整对照，向数据方补齐</t>
+          <t>引用「29 组」而非旧文档的「27 组」；L1-22 带预置脱粘、L1-23 是两级载荷，见 details.md §45</t>
         </is>
       </c>
     </row>

--- a/l1/L1数据记录.xlsx
+++ b/l1/L1数据记录.xlsx
@@ -620,7 +620,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>有(33)</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>有(60)</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>有(31)</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>有(41)</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>有(30)</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>有(49)</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>有(44)</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>有(69)</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1516,7 +1516,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>有(93)</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>有(48)</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>有(318)</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>有(94)</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>有(253)</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>有(4)</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>有(192)</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>有(1)</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>有(103)</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -2524,7 +2524,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>有(1)</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -2636,7 +2636,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>有(344)</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>有(218)</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -3820,12 +3820,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>AE(.pridb) + FBG + LUNA(DFOS)</t>
+          <t>AE(.pridb) + FBG + LUNA(DFOS) + PZT(导波, PZT-&lt;N&gt;)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>论文 Broer 2021 Level1–4 复现对象；唯一同时有 AE+FBG+DFOS 的一组</t>
+          <t>论文 Broer 2021 Level1–4 复现对象；四类传感齐全（AE+FBG+DFOS+PZT）</t>
         </is>
       </c>
     </row>
@@ -3867,12 +3867,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>AE(.pridb) + LUNA(DFOS)；无 FBG</t>
+          <t>AE(.pridb) + LUNA(DFOS)；无 FBG、无 PZT</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>已判定「不支持跨试件统一阈值的在线预警」：组间 AE 事件率相差 3 倍以上，自适应阈值反而比固定阈值差</t>
+          <t>已判定「不支持跨试件统一阈值的在线预警」：组间 AE 事件率相差 3 倍以上，自适应阈值反而比固定阈值差；C2 九组均无 PZT</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3914,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>AE(.DTA, Mistras AEwin) + FBG(sm130, 5 Hz)</t>
+          <t>AE(.DTA, Mistras AEwin) + FBG(sm130, 5 Hz) + PZT(导波, 目录名 `PZT/`)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>AE(.DTA, Mistras AEwin) + FBG(sm130, 10 Hz)</t>
+          <t>AE(.DTA, Mistras AEwin) + FBG(sm130, 10 Hz) + PZT(导波, 目录名 `PZT-&lt;N&gt;/`)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -3981,7 +3981,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F78"/>
+  <dimension ref="A1:F142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4113,25 +4113,25 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>(组根)</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>4</v>
-      </c>
-      <c r="E5" t="n">
-        <v>807.5</v>
-      </c>
+          <t>PZT-1</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>(未逐文件统计)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>.csv×3, .pdf×1</t>
+          <t>每个 State_* 下 &lt;频率&gt;/Actionneur&lt;N&gt;/measured_data_rep_*.mat（6 频 × 8 发 × 10 重复 = 480 个）；本会话状态数 1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L1-04</t>
+          <t>L1-03</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -4141,25 +4141,25 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AE</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>2</v>
-      </c>
-      <c r="E6" t="n">
-        <v>260.4</v>
-      </c>
+          <t>PZT-2</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>(未逐文件统计)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>.pridb×2</t>
+          <t>每个 State_* 下 &lt;频率&gt;/Actionneur&lt;N&gt;/measured_data_rep_*.mat（6 频 × 8 发 × 10 重复 = 480 个）；本会话状态数 32</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L1-04</t>
+          <t>L1-03</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -4169,18 +4169,18 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FBG</t>
+          <t>(组根)</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E7" t="n">
-        <v>122.6</v>
+        <v>807.5</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>.txt×1</t>
+          <t>.csv×3, .pdf×1</t>
         </is>
       </c>
     </row>
@@ -4197,18 +4197,18 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>LUNA</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>48.3</v>
+        <v>260.4</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>.txt×2</t>
+          <t>.pridb×2</t>
         </is>
       </c>
     </row>
@@ -4225,25 +4225,25 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>(组根)</t>
+          <t>FBG</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>694.6</v>
+        <v>122.6</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>.csv×3, .pdf×1</t>
+          <t>.txt×1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>L1-05</t>
+          <t>L1-04</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4253,25 +4253,25 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>LUNA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>111.6</v>
+        <v>48.3</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>.pridb×1</t>
+          <t>.txt×2</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>L1-05</t>
+          <t>L1-04</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4281,25 +4281,25 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>FBG</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" t="n">
-        <v>65.2</v>
-      </c>
+          <t>PZT-1</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>(未逐文件统计)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>.txt×1</t>
+          <t>每个 State_* 下 &lt;频率&gt;/Actionneur&lt;N&gt;/measured_data_rep_*.mat（6 频 × 8 发 × 10 重复 = 480 个）；本会话状态数 1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>L1-05</t>
+          <t>L1-04</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -4309,25 +4309,25 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>LUNA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>2</v>
-      </c>
-      <c r="E12" t="n">
-        <v>25.9</v>
-      </c>
+          <t>PZT-2</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>(未逐文件统计)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>.txt×2</t>
+          <t>每个 State_* 下 &lt;频率&gt;/Actionneur&lt;N&gt;/measured_data_rep_*.mat（6 频 × 8 发 × 10 重复 = 480 个）；本会话状态数 1</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>L1-05</t>
+          <t>L1-04</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -4337,81 +4337,81 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>(组根)</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>4</v>
-      </c>
-      <c r="E13" t="n">
-        <v>213</v>
-      </c>
+          <t>PZT-3</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>(未逐文件统计)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>.csv×3, .pdf×1</t>
+          <t>每个 State_* 下 &lt;频率&gt;/Actionneur&lt;N&gt;/measured_data_rep_*.mat（6 频 × 8 发 × 10 重复 = 480 个）；本会话状态数 58</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>L1-06</t>
+          <t>L1-04</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>L1 变幅VA+FBG</t>
+          <t>L1 恒幅+FBG+DFOS</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>(组根)</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E14" t="n">
-        <v>274.5</v>
+        <v>694.6</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>.dta×1</t>
+          <t>.csv×3, .pdf×1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>L1-06</t>
+          <t>L1-05</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>L1 变幅VA+FBG</t>
+          <t>L1 恒幅+FBG+DFOS</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>FBG</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>32.8</v>
+        <v>111.6</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>.txt×2</t>
+          <t>.pridb×1</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>L1-09</t>
+          <t>L1-05</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4421,25 +4421,25 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>FBG</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>126.5</v>
+        <v>65.2</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>.pridb×1</t>
+          <t>.txt×1</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>L1-09</t>
+          <t>L1-05</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4449,25 +4449,25 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>FBG</t>
+          <t>LUNA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E17" t="n">
-        <v>52.9</v>
+        <v>25.9</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>.txt×1</t>
+          <t>.txt×2</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>L1-09</t>
+          <t>L1-05</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4477,25 +4477,25 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>LUNA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>1</v>
-      </c>
-      <c r="E18" t="n">
-        <v>17.4</v>
-      </c>
+          <t>PZT-1</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>(未逐文件统计)</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>.txt×1</t>
+          <t>每个 State_* 下 &lt;频率&gt;/Actionneur&lt;N&gt;/measured_data_rep_*.mat（6 频 × 8 发 × 10 重复 = 480 个）；本会话状态数 1</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>L1-09</t>
+          <t>L1-05</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4505,53 +4505,53 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>(组根)</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>4</v>
-      </c>
-      <c r="E19" t="n">
-        <v>240.9</v>
-      </c>
+          <t>PZT-2</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>(未逐文件统计)</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>.csv×3, .pdf×1</t>
+          <t>每个 State_* 下 &lt;频率&gt;/Actionneur&lt;N&gt;/measured_data_rep_*.mat（6 频 × 8 发 × 10 重复 = 480 个）；本会话状态数 30</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>L1-13</t>
+          <t>L1-05</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>L1 变幅VA+FBG</t>
+          <t>L1 恒幅+FBG+DFOS</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>(组根)</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E20" t="n">
-        <v>459.3</v>
+        <v>213</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>.dta×1</t>
+          <t>.csv×3, .pdf×1</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>L1-13</t>
+          <t>L1-06</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4561,25 +4561,25 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>FBG</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>25.8</v>
+        <v>274.5</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>.txt×1</t>
+          <t>.dta×1</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>L1-14</t>
+          <t>L1-06</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4589,25 +4589,25 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>FBG</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E22" t="n">
-        <v>585.9</v>
+        <v>32.8</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>.dta×1</t>
+          <t>.txt×2</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>L1-14</t>
+          <t>L1-06</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4617,30 +4617,30 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>FBG</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>1</v>
-      </c>
-      <c r="E23" t="n">
-        <v>30.7</v>
-      </c>
+          <t>PZT</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>(未逐文件统计)</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>.txt×1</t>
+          <t>每个 State_* 下 &lt;频率&gt;/Actionneur&lt;N&gt;/measured_data_rep_*.mat（6 频 × 8 发 × 10 重复 = 480 个）；本会话状态数 41</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>L1-22</t>
+          <t>L1-09</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>L1 变幅VA+FBG</t>
+          <t>L1 恒幅+FBG+DFOS</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -4649,26 +4649,26 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>19762.7</v>
+        <v>126.5</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>.dta×11</t>
+          <t>.pridb×1</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>L1-22</t>
+          <t>L1-09</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>L1 变幅VA+FBG</t>
+          <t>L1 恒幅+FBG+DFOS</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -4677,21 +4677,21 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>65</v>
+        <v>52.9</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>.txt×2</t>
+          <t>.txt×1</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>L1-23</t>
+          <t>L1-09</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -4701,25 +4701,25 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>LUNA</t>
         </is>
       </c>
       <c r="D26" t="n">
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>1770.9</v>
+        <v>17.4</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>.pridb×1</t>
+          <t>.txt×1</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>L1-23</t>
+          <t>L1-09</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -4729,25 +4729,25 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>FBG</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>5</v>
-      </c>
-      <c r="E27" t="n">
-        <v>168.2</v>
-      </c>
+          <t>PZT-1</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>(未逐文件统计)</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>.txt×5</t>
+          <t>每个 State_* 下 &lt;频率&gt;/Actionneur&lt;N&gt;/measured_data_rep_*.mat（6 频 × 8 发 × 10 重复 = 480 个）；本会话状态数 1</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>L1-23</t>
+          <t>L1-09</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -4757,25 +4757,25 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>LUNA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>2</v>
-      </c>
-      <c r="E28" t="n">
-        <v>58.6</v>
-      </c>
+          <t>PZT-2</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>(未逐文件统计)</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>.txt×2</t>
+          <t>每个 State_* 下 &lt;频率&gt;/Actionneur&lt;N&gt;/measured_data_rep_*.mat（6 频 × 8 发 × 10 重复 = 480 个）；本会话状态数 1</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>L1-23</t>
+          <t>L1-09</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -4785,53 +4785,53 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>(组根)</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>4</v>
-      </c>
-      <c r="E29" t="n">
-        <v>4415.4</v>
-      </c>
+          <t>PZT-3</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>(未逐文件统计)</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>.csv×3, .pdf×1</t>
+          <t>每个 State_* 下 &lt;频率&gt;/Actionneur&lt;N&gt;/measured_data_rep_*.mat（6 频 × 8 发 × 10 重复 = 480 个）；本会话状态数 28</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>L1-24</t>
+          <t>L1-09</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>L1 变幅VA+FBG</t>
+          <t>L1 恒幅+FBG+DFOS</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>(组根)</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E30" t="n">
-        <v>197.3</v>
+        <v>240.9</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>.dta×1</t>
+          <t>.csv×3, .pdf×1</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>L1-24</t>
+          <t>L1-13</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -4841,86 +4841,86 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>FBG</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>67.8</v>
+        <v>459.3</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>.txt×2</t>
+          <t>.dta×1</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>L1-25</t>
+          <t>L1-13</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>L1 谱载+FBG</t>
+          <t>L1 变幅VA+FBG</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>FBG</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>420.7</v>
+        <v>25.8</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>.dta×2</t>
+          <t>.txt×1</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>L1-25</t>
+          <t>L1-13</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>L1 谱载+FBG</t>
+          <t>L1 变幅VA+FBG</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>FBG</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>3071</v>
-      </c>
-      <c r="E33" t="n">
-        <v>138.3</v>
-      </c>
+          <t>PZT</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>(未逐文件统计)</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>.txt×3071</t>
+          <t>每个 State_* 下 &lt;频率&gt;/Actionneur&lt;N&gt;/measured_data_rep_*.mat（6 频 × 8 发 × 10 重复 = 480 个）；本会话状态数 49</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>L1-27</t>
+          <t>L1-14</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>L1 谱载+FBG</t>
+          <t>L1 变幅VA+FBG</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4932,7 +4932,7 @@
         <v>1</v>
       </c>
       <c r="E34" t="n">
-        <v>1128.9</v>
+        <v>585.9</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4943,12 +4943,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>L1-27</t>
+          <t>L1-14</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>L1 谱载+FBG</t>
+          <t>L1 变幅VA+FBG</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -4957,138 +4957,138 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1020</v>
+        <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>46.2</v>
+        <v>30.7</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>.txt×1020</t>
+          <t>.txt×1</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>L1-29</t>
+          <t>L1-14</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>L1 谱载+FBG</t>
+          <t>L1 变幅VA+FBG</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>AE</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>1</v>
-      </c>
-      <c r="E36" t="n">
-        <v>395.1</v>
-      </c>
+          <t>PZT</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>(未逐文件统计)</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>.dta×1</t>
+          <t>每个 State_* 下 &lt;频率&gt;/Actionneur&lt;N&gt;/measured_data_rep_*.mat（6 频 × 8 发 × 10 重复 = 480 个）；本会话状态数 44</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>L1-29</t>
+          <t>L1-22</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>L1 谱载+FBG</t>
+          <t>L1 变幅VA+FBG</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>FBG</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>3105</v>
+        <v>11</v>
       </c>
       <c r="E37" t="n">
-        <v>101.6</v>
+        <v>19762.7</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>.txt×3105</t>
+          <t>.dta×11</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>L1-30</t>
+          <t>L1-22</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>L1 谱载+FBG</t>
+          <t>L1 变幅VA+FBG</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>FBG</t>
         </is>
       </c>
       <c r="D38" t="n">
         <v>2</v>
       </c>
       <c r="E38" t="n">
-        <v>0.8</v>
+        <v>65</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>.dta×2</t>
+          <t>.txt×2</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>L1-30</t>
+          <t>L1-22</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>L1 谱载+FBG</t>
+          <t>L1 变幅VA+FBG</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>FBG</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>27</v>
-      </c>
-      <c r="E39" t="n">
-        <v>1.3</v>
-      </c>
+          <t>PZT</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>(未逐文件统计)</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>.txt×27</t>
+          <t>每个 State_* 下 &lt;频率&gt;/Actionneur&lt;N&gt;/measured_data_rep_*.mat（6 频 × 8 发 × 10 重复 = 480 个）；本会话状态数 69</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>L1-31</t>
+          <t>L1-23</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>L1 谱载+FBG</t>
+          <t>L1 恒幅+FBG+DFOS</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5097,26 +5097,26 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E40" t="n">
-        <v>726.8</v>
+        <v>1770.9</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>.dta×2</t>
+          <t>.pridb×1</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>L1-31</t>
+          <t>L1-23</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>L1 谱载+FBG</t>
+          <t>L1 恒幅+FBG+DFOS</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5125,194 +5125,194 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>2420</v>
+        <v>5</v>
       </c>
       <c r="E41" t="n">
-        <v>107.8</v>
+        <v>168.2</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>.txt×2420</t>
+          <t>.txt×5</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>L1-34</t>
+          <t>L1-23</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>L1 谱载+FBG</t>
+          <t>L1 恒幅+FBG+DFOS</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>LUNA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>1.5</v>
+        <v>58.6</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>.dta×1</t>
+          <t>.txt×2</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>L1-34</t>
+          <t>L1-23</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>L1 谱载+FBG</t>
+          <t>L1 恒幅+FBG+DFOS</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>FBG</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>2</v>
-      </c>
-      <c r="E43" t="n">
-        <v>0.1</v>
-      </c>
+          <t>PZT-1</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>(未逐文件统计)</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>.txt×2</t>
+          <t>每个 State_* 下 &lt;频率&gt;/Actionneur&lt;N&gt;/measured_data_rep_*.mat（6 频 × 8 发 × 10 重复 = 480 个）；本会话状态数 16</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>L1-35</t>
+          <t>L1-23</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>L1 谱载+FBG</t>
+          <t>L1 恒幅+FBG+DFOS</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>AE</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>8</v>
-      </c>
-      <c r="E44" t="n">
-        <v>901.3</v>
-      </c>
+          <t>PZT-2</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>(未逐文件统计)</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>.dta×8</t>
+          <t>每个 State_* 下 &lt;频率&gt;/Actionneur&lt;N&gt;/measured_data_rep_*.mat（6 频 × 8 发 × 10 重复 = 480 个）；本会话状态数 7</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>L1-35</t>
+          <t>L1-23</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>L1 谱载+FBG</t>
+          <t>L1 恒幅+FBG+DFOS</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>FBG</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>1779</v>
-      </c>
-      <c r="E45" t="n">
-        <v>81.90000000000001</v>
-      </c>
+          <t>PZT-3</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>(未逐文件统计)</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>.txt×1779</t>
+          <t>每个 State_* 下 &lt;频率&gt;/Actionneur&lt;N&gt;/measured_data_rep_*.mat（6 频 × 8 发 × 10 重复 = 480 个）；本会话状态数 30</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>L1-36</t>
+          <t>L1-23</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>L1 谱载+FBG</t>
+          <t>L1 恒幅+FBG+DFOS</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>AE</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E46" t="n">
-        <v>10.2</v>
-      </c>
+          <t>PZT-4</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>(未逐文件统计)</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>.dta×1</t>
+          <t>每个 State_* 下 &lt;频率&gt;/Actionneur&lt;N&gt;/measured_data_rep_*.mat（6 频 × 8 发 × 10 重复 = 480 个）；本会话状态数 40</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>L1-36</t>
+          <t>L1-23</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>L1 谱载+FBG</t>
+          <t>L1 恒幅+FBG+DFOS</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>FBG</t>
+          <t>(组根)</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E47" t="n">
-        <v>0.4</v>
+        <v>4415.4</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>.txt×10</t>
+          <t>.csv×3, .pdf×1</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>L1-41</t>
+          <t>L1-24</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>L1 谱载+FBG</t>
+          <t>L1 变幅VA+FBG</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -5324,7 +5324,7 @@
         <v>1</v>
       </c>
       <c r="E48" t="n">
-        <v>217</v>
+        <v>197.3</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5335,12 +5335,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>L1-41</t>
+          <t>L1-24</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>L1 谱载+FBG</t>
+          <t>L1 变幅VA+FBG</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -5349,49 +5349,49 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>2688</v>
+        <v>2</v>
       </c>
       <c r="E49" t="n">
-        <v>119</v>
+        <v>67.8</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>.txt×2688</t>
+          <t>.txt×2</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>L1-44</t>
+          <t>L1-24</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>L1 谱载+FBG</t>
+          <t>L1 变幅VA+FBG</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>AE</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>3</v>
-      </c>
-      <c r="E50" t="n">
-        <v>3456.2</v>
-      </c>
+          <t>PZT</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>(未逐文件统计)</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>.dta×3</t>
+          <t>每个 State_* 下 &lt;频率&gt;/Actionneur&lt;N&gt;/measured_data_rep_*.mat（6 频 × 8 发 × 10 重复 = 480 个）；本会话状态数 48</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>L1-44</t>
+          <t>L1-25</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5401,422 +5401,422 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>FBG</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1849</v>
+        <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>111</v>
+        <v>420.7</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>.txt×1849</t>
+          <t>.dta×2</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>L1-49</t>
+          <t>L1-25</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>L1 恒幅+DFOS</t>
+          <t>L1 谱载+FBG</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>FBG</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1</v>
+        <v>3071</v>
       </c>
       <c r="E52" t="n">
-        <v>285.6</v>
+        <v>138.3</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>.pridb×1</t>
+          <t>.txt×3071</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>L1-49</t>
+          <t>L1-25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>L1 恒幅+DFOS</t>
+          <t>L1 谱载+FBG</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>LUNA</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>2</v>
-      </c>
-      <c r="E53" t="n">
-        <v>117.7</v>
-      </c>
+          <t>PZT-1</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>(未逐文件统计)</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>.txt×2</t>
+          <t>每个 State_* 下 &lt;频率&gt;/Actionneur&lt;N&gt;/measured_data_rep_*.mat（6 频 × 8 发 × 10 重复 = 480 个）；本会话状态数 180</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>L1-49</t>
+          <t>L1-25</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>L1 恒幅+DFOS</t>
+          <t>L1 谱载+FBG</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>(组根)</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>6</v>
-      </c>
-      <c r="E54" t="n">
-        <v>4.7</v>
-      </c>
+          <t>PZT-2</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>(未逐文件统计)</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>.csv×5, .pdf×1</t>
+          <t>每个 State_* 下 &lt;频率&gt;/Actionneur&lt;N&gt;/measured_data_rep_*.mat（6 频 × 8 发 × 10 重复 = 480 个）；本会话状态数 30</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>L1-50</t>
+          <t>L1-25</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>L1 恒幅+DFOS</t>
+          <t>L1 谱载+FBG</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>AE</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>1</v>
-      </c>
-      <c r="E55" t="n">
-        <v>210.5</v>
-      </c>
+          <t>PZT-3</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>(未逐文件统计)</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>.pridb×1</t>
+          <t>每个 State_* 下 &lt;频率&gt;/Actionneur&lt;N&gt;/measured_data_rep_*.mat（6 频 × 8 发 × 10 重复 = 480 个）；本会话状态数 108</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>L1-50</t>
+          <t>L1-25</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>L1 恒幅+DFOS</t>
+          <t>L1 谱载+FBG</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>LUNA</t>
+          <t>(组根)</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>541.6</v>
+        <v>0</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>.txt×3</t>
+          <t>.txt×1</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>L1-50</t>
+          <t>L1-27</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>L1 恒幅+DFOS</t>
+          <t>L1 谱载+FBG</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>(组根)</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E57" t="n">
-        <v>5.9</v>
+        <v>1128.9</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>.csv×5, .pdf×1</t>
+          <t>.dta×1</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>L1-51</t>
+          <t>L1-27</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>L1 恒幅+DFOS</t>
+          <t>L1 谱载+FBG</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>FBG</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1</v>
+        <v>1020</v>
       </c>
       <c r="E58" t="n">
-        <v>521.5</v>
+        <v>46.2</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>.pridb×1</t>
+          <t>.txt×1020</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>L1-51</t>
+          <t>L1-27</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>L1 恒幅+DFOS</t>
+          <t>L1 谱载+FBG</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>LUNA</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>2</v>
-      </c>
-      <c r="E59" t="n">
-        <v>963.9</v>
-      </c>
+          <t>PZT-1</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>(未逐文件统计)</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>.txt×2</t>
+          <t>每个 State_* 下 &lt;频率&gt;/Actionneur&lt;N&gt;/measured_data_rep_*.mat（6 频 × 8 发 × 10 重复 = 480 个）；本会话状态数 29</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>L1-51</t>
+          <t>L1-27</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>L1 恒幅+DFOS</t>
+          <t>L1 谱载+FBG</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>(组根)</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>6</v>
-      </c>
-      <c r="E60" t="n">
-        <v>11.5</v>
-      </c>
+          <t>PZT-2</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>(未逐文件统计)</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>.csv×5, .pdf×1</t>
+          <t>每个 State_* 下 &lt;频率&gt;/Actionneur&lt;N&gt;/measured_data_rep_*.mat（6 频 × 8 发 × 10 重复 = 480 个）；本会话状态数 21</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>L1-52</t>
+          <t>L1-27</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>L1 恒幅+DFOS</t>
+          <t>L1 谱载+FBG</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>AE</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>1</v>
-      </c>
-      <c r="E61" t="n">
-        <v>1426</v>
-      </c>
+          <t>PZT-3</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>(未逐文件统计)</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
-          <t>.pridb×1</t>
+          <t>每个 State_* 下 &lt;频率&gt;/Actionneur&lt;N&gt;/measured_data_rep_*.mat（6 频 × 8 发 × 10 重复 = 480 个）；本会话状态数 31</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>L1-52</t>
+          <t>L1-27</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>L1 恒幅+DFOS</t>
+          <t>L1 谱载+FBG</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>LUNA</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>1</v>
-      </c>
-      <c r="E62" t="n">
-        <v>4325.7</v>
-      </c>
+          <t>PZT-4</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>(未逐文件统计)</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
-          <t>.txt×1</t>
+          <t>每个 State_* 下 &lt;频率&gt;/Actionneur&lt;N&gt;/measured_data_rep_*.mat（6 频 × 8 发 × 10 重复 = 480 个）；本会话状态数 13</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>L1-52</t>
+          <t>L1-27</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>L1 恒幅+DFOS</t>
+          <t>L1 谱载+FBG</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>(组根)</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>6</v>
-      </c>
-      <c r="E63" t="n">
-        <v>33</v>
-      </c>
+          <t>PZT-5</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>(未逐文件统计)</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>.csv×5, .pdf×1</t>
+          <t>每个 State_* 下 &lt;频率&gt;/Actionneur&lt;N&gt;/measured_data_rep_*.mat（6 频 × 8 发 × 10 重复 = 480 个）；本会话状态数 0</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>L1-54</t>
+          <t>L1-27</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>L1 恒幅+DFOS</t>
+          <t>L1 谱载+FBG</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>AE</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>1</v>
-      </c>
-      <c r="E64" t="n">
-        <v>2196.1</v>
-      </c>
+          <t>PZT-6</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>(未逐文件统计)</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
-          <t>.pridb×1</t>
+          <t>每个 State_* 下 &lt;频率&gt;/Actionneur&lt;N&gt;/measured_data_rep_*.mat（6 频 × 8 发 × 10 重复 = 480 个）；本会话状态数 0</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>L1-54</t>
+          <t>L1-27</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>L1 恒幅+DFOS</t>
+          <t>L1 谱载+FBG</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>LUNA</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>1</v>
-      </c>
-      <c r="E65" t="n">
-        <v>5363.3</v>
-      </c>
+          <t>PZT-7</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>(未逐文件统计)</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
-          <t>.txt×1</t>
+          <t>每个 State_* 下 &lt;频率&gt;/Actionneur&lt;N&gt;/measured_data_rep_*.mat（6 频 × 8 发 × 10 重复 = 480 个）；本会话状态数 0</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>L1-54</t>
+          <t>L1-27</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>L1 恒幅+DFOS</t>
+          <t>L1 谱载+FBG</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -5825,26 +5825,26 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E66" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>.csv×5, .pdf×1</t>
+          <t>.txt×1</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>L1-55</t>
+          <t>L1-29</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>L1 恒幅+DFOS</t>
+          <t>L1 谱载+FBG</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -5856,135 +5856,135 @@
         <v>1</v>
       </c>
       <c r="E67" t="n">
-        <v>456.9</v>
+        <v>395.1</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>.pridb×1</t>
+          <t>.dta×1</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>L1-55</t>
+          <t>L1-29</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>L1 恒幅+DFOS</t>
+          <t>L1 谱载+FBG</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>LUNA</t>
+          <t>FBG</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>3</v>
+        <v>3105</v>
       </c>
       <c r="E68" t="n">
-        <v>2214.9</v>
+        <v>101.6</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>.txt×3</t>
+          <t>.txt×3105</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>L1-55</t>
+          <t>L1-29</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>L1 恒幅+DFOS</t>
+          <t>L1 谱载+FBG</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>(组根)</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>6</v>
-      </c>
-      <c r="E69" t="n">
-        <v>19.1</v>
-      </c>
+          <t>PZT-1</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>(未逐文件统计)</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
-          <t>.csv×5, .pdf×1</t>
+          <t>每个 State_* 下 &lt;频率&gt;/Actionneur&lt;N&gt;/measured_data_rep_*.mat（6 频 × 8 发 × 10 重复 = 480 个）；本会话状态数 68</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>L1-56</t>
+          <t>L1-29</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>L1 恒幅+DFOS</t>
+          <t>L1 谱载+FBG</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>AE</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>1</v>
-      </c>
-      <c r="E70" t="n">
-        <v>2532</v>
-      </c>
+          <t>PZT-2</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>(未逐文件统计)</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
-          <t>.pridb×1</t>
+          <t>每个 State_* 下 &lt;频率&gt;/Actionneur&lt;N&gt;/measured_data_rep_*.mat（6 频 × 8 发 × 10 重复 = 480 个）；本会话状态数 180</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>L1-56</t>
+          <t>L1-29</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>L1 恒幅+DFOS</t>
+          <t>L1 谱载+FBG</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>LUNA</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>2</v>
-      </c>
-      <c r="E71" t="n">
-        <v>1883.8</v>
-      </c>
+          <t>PZT-3</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>(未逐文件统计)</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>.txt×2</t>
+          <t>每个 State_* 下 &lt;频率&gt;/Actionneur&lt;N&gt;/measured_data_rep_*.mat（6 频 × 8 发 × 10 重复 = 480 个）；本会话状态数 5</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>L1-56</t>
+          <t>L1-29</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>L1 恒幅+DFOS</t>
+          <t>L1 谱载+FBG</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -5993,26 +5993,26 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E72" t="n">
-        <v>25.6</v>
+        <v>0</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>.csv×5, .pdf×1</t>
+          <t>.txt×1</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>L1-59</t>
+          <t>L1-30</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>L1 恒幅+DFOS</t>
+          <t>L1 谱载+FBG</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -6024,149 +6024,1941 @@
         <v>2</v>
       </c>
       <c r="E73" t="n">
-        <v>510.1</v>
+        <v>0.8</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>.pridb×2</t>
+          <t>.dta×2</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>L1-59</t>
+          <t>L1-30</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>L1 恒幅+DFOS</t>
+          <t>L1 谱载+FBG</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>LUNA</t>
+          <t>FBG</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="E74" t="n">
-        <v>1042.7</v>
+        <v>1.3</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>.txt×3</t>
+          <t>.txt×27</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>L1-59</t>
+          <t>L1-30</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>L1 恒幅+DFOS</t>
+          <t>L1 谱载+FBG</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>(组根)</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>6</v>
-      </c>
-      <c r="E75" t="n">
-        <v>10</v>
-      </c>
+          <t>PZT-1</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>(未逐文件统计)</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
-          <t>.csv×5, .pdf×1</t>
+          <t>每个 State_* 下 &lt;频率&gt;/Actionneur&lt;N&gt;/measured_data_rep_*.mat（6 频 × 8 发 × 10 重复 = 480 个）；本会话状态数 3</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>L1-60</t>
+          <t>L1-30</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>L1 恒幅+DFOS</t>
+          <t>L1 谱载+FBG</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>AE</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>1</v>
-      </c>
-      <c r="E76" t="n">
-        <v>963.9</v>
-      </c>
+          <t>PZT-2</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>(未逐文件统计)</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
-          <t>.pridb×1</t>
+          <t>每个 State_* 下 &lt;频率&gt;/Actionneur&lt;N&gt;/measured_data_rep_*.mat（6 频 × 8 发 × 10 重复 = 480 个）；本会话状态数 1</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>L1-60</t>
+          <t>L1-30</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>L1 恒幅+DFOS</t>
+          <t>L1 谱载+FBG</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>LUNA</t>
+          <t>(组根)</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>1658.7</v>
+        <v>0</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>.txt×2</t>
+          <t>.txt×1</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
+          <t>L1-31</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>L1 谱载+FBG</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>2</v>
+      </c>
+      <c r="E78" t="n">
+        <v>726.8</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>.dta×2</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>L1-31</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>L1 谱载+FBG</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>FBG</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>2420</v>
+      </c>
+      <c r="E79" t="n">
+        <v>107.8</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>.txt×2420</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>L1-31</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>L1 谱载+FBG</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>PZT-1</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>(未逐文件统计)</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>每个 State_* 下 &lt;频率&gt;/Actionneur&lt;N&gt;/measured_data_rep_*.mat（6 频 × 8 发 × 10 重复 = 480 个）；本会话状态数 97</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>L1-31</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>L1 谱载+FBG</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>PZT-2</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>(未逐文件统计)</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>每个 State_* 下 &lt;频率&gt;/Actionneur&lt;N&gt;/measured_data_rep_*.mat（6 频 × 8 发 × 10 重复 = 480 个）；本会话状态数 95</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>L1-31</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>L1 谱载+FBG</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>(组根)</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>1</v>
+      </c>
+      <c r="E82" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>.txt×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>L1-34</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>L1 谱载+FBG</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>1</v>
+      </c>
+      <c r="E83" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>.dta×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>L1-34</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>L1 谱载+FBG</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>FBG</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>2</v>
+      </c>
+      <c r="E84" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>.txt×2</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>L1-34</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>L1 谱载+FBG</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>PZT</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>(未逐文件统计)</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>每个 State_* 下 &lt;频率&gt;/Actionneur&lt;N&gt;/measured_data_rep_*.mat（6 频 × 8 发 × 10 重复 = 480 个）；本会话状态数 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>L1-34</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>L1 谱载+FBG</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>(组根)</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>1</v>
+      </c>
+      <c r="E86" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>.txt×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>L1-35</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>L1 谱载+FBG</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>8</v>
+      </c>
+      <c r="E87" t="n">
+        <v>901.3</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>.dta×8</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>L1-35</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>L1 谱载+FBG</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>FBG</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>1779</v>
+      </c>
+      <c r="E88" t="n">
+        <v>81.90000000000001</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>.txt×1779</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>L1-35</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>L1 谱载+FBG</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>PZT-1</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>(未逐文件统计)</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>每个 State_* 下 &lt;频率&gt;/Actionneur&lt;N&gt;/measured_data_rep_*.mat（6 频 × 8 发 × 10 重复 = 480 个）；本会话状态数 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>L1-35</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>L1 谱载+FBG</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>PZT-10</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>(未逐文件统计)</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>每个 State_* 下 &lt;频率&gt;/Actionneur&lt;N&gt;/measured_data_rep_*.mat（6 频 × 8 发 × 10 重复 = 480 个）；本会话状态数 25</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>L1-35</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>L1 谱载+FBG</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>PZT-2</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>(未逐文件统计)</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>每个 State_* 下 &lt;频率&gt;/Actionneur&lt;N&gt;/measured_data_rep_*.mat（6 频 × 8 发 × 10 重复 = 480 个）；本会话状态数 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>L1-35</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>L1 谱载+FBG</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>PZT-3</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>(未逐文件统计)</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>每个 State_* 下 &lt;频率&gt;/Actionneur&lt;N&gt;/measured_data_rep_*.mat（6 频 × 8 发 × 10 重复 = 480 个）；本会话状态数 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>L1-35</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>L1 谱载+FBG</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>PZT-4</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>(未逐文件统计)</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>每个 State_* 下 &lt;频率&gt;/Actionneur&lt;N&gt;/measured_data_rep_*.mat（6 频 × 8 发 × 10 重复 = 480 个）；本会话状态数 16</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>L1-35</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>L1 谱载+FBG</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>PZT-5</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>(未逐文件统计)</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>每个 State_* 下 &lt;频率&gt;/Actionneur&lt;N&gt;/measured_data_rep_*.mat（6 频 × 8 发 × 10 重复 = 480 个）；本会话状态数 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>L1-35</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>L1 谱载+FBG</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>PZT-6</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>(未逐文件统计)</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>每个 State_* 下 &lt;频率&gt;/Actionneur&lt;N&gt;/measured_data_rep_*.mat（6 频 × 8 发 × 10 重复 = 480 个）；本会话状态数 23</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>L1-35</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>L1 谱载+FBG</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>PZT-7</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>(未逐文件统计)</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>每个 State_* 下 &lt;频率&gt;/Actionneur&lt;N&gt;/measured_data_rep_*.mat（6 频 × 8 发 × 10 重复 = 480 个）；本会话状态数 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>L1-35</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>L1 谱载+FBG</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>PZT-8</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>(未逐文件统计)</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>每个 State_* 下 &lt;频率&gt;/Actionneur&lt;N&gt;/measured_data_rep_*.mat（6 频 × 8 发 × 10 重复 = 480 个）；本会话状态数 21</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>L1-35</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>L1 谱载+FBG</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>PZT-9</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>(未逐文件统计)</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>每个 State_* 下 &lt;频率&gt;/Actionneur&lt;N&gt;/measured_data_rep_*.mat（6 频 × 8 发 × 10 重复 = 480 个）；本会话状态数 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>L1-35</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>L1 谱载+FBG</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>(组根)</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>1</v>
+      </c>
+      <c r="E99" t="n">
+        <v>0</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>.txt×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>L1-36</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>L1 谱载+FBG</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>1</v>
+      </c>
+      <c r="E100" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>.dta×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>L1-36</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>L1 谱载+FBG</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>FBG</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>10</v>
+      </c>
+      <c r="E101" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>.txt×10</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>L1-36</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>L1 谱载+FBG</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>PZT</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>(未逐文件统计)</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>每个 State_* 下 &lt;频率&gt;/Actionneur&lt;N&gt;/measured_data_rep_*.mat（6 频 × 8 发 × 10 重复 = 480 个）；本会话状态数 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>L1-36</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>L1 谱载+FBG</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>(组根)</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>1</v>
+      </c>
+      <c r="E103" t="n">
+        <v>0</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>.txt×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>L1-41</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>L1 谱载+FBG</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>1</v>
+      </c>
+      <c r="E104" t="n">
+        <v>217</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>.dta×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>L1-41</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>L1 谱载+FBG</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>FBG</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>2688</v>
+      </c>
+      <c r="E105" t="n">
+        <v>119</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>.txt×2688</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>L1-41</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>L1 谱载+FBG</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>PZT-1</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>(未逐文件统计)</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>每个 State_* 下 &lt;频率&gt;/Actionneur&lt;N&gt;/measured_data_rep_*.mat（6 频 × 8 发 × 10 重复 = 480 个）；本会话状态数 180</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>L1-41</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>L1 谱载+FBG</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>PZT-2</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>(未逐文件统计)</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>每个 State_* 下 &lt;频率&gt;/Actionneur&lt;N&gt;/measured_data_rep_*.mat（6 频 × 8 发 × 10 重复 = 480 个）；本会话状态数 164</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>L1-41</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>L1 谱载+FBG</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>(组根)</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>1</v>
+      </c>
+      <c r="E108" t="n">
+        <v>0</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>.txt×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>L1-44</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>L1 谱载+FBG</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>3</v>
+      </c>
+      <c r="E109" t="n">
+        <v>3456.2</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>.dta×3</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>L1-44</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>L1 谱载+FBG</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>FBG</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>1849</v>
+      </c>
+      <c r="E110" t="n">
+        <v>111</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>.txt×1849</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>L1-44</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>L1 谱载+FBG</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>PZT-1</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>(未逐文件统计)</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr"/>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>每个 State_* 下 &lt;频率&gt;/Actionneur&lt;N&gt;/measured_data_rep_*.mat（6 频 × 8 发 × 10 重复 = 480 个）；本会话状态数 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>L1-44</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>L1 谱载+FBG</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>PZT-2</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>(未逐文件统计)</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>每个 State_* 下 &lt;频率&gt;/Actionneur&lt;N&gt;/measured_data_rep_*.mat（6 频 × 8 发 × 10 重复 = 480 个）；本会话状态数 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>L1-44</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>L1 谱载+FBG</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>PZT-3</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>(未逐文件统计)</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr"/>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>每个 State_* 下 &lt;频率&gt;/Actionneur&lt;N&gt;/measured_data_rep_*.mat（6 频 × 8 发 × 10 重复 = 480 个）；本会话状态数 180</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>L1-44</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>L1 谱载+FBG</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>PZT-4</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>(未逐文件统计)</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr"/>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>每个 State_* 下 &lt;频率&gt;/Actionneur&lt;N&gt;/measured_data_rep_*.mat（6 频 × 8 发 × 10 重复 = 480 个）；本会话状态数 37</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>L1-44</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>L1 谱载+FBG</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>(组根)</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>1</v>
+      </c>
+      <c r="E115" t="n">
+        <v>0</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>.txt×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>L1-49</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>L1 恒幅+DFOS</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>1</v>
+      </c>
+      <c r="E116" t="n">
+        <v>285.6</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>.pridb×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>L1-49</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>L1 恒幅+DFOS</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>LUNA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>2</v>
+      </c>
+      <c r="E117" t="n">
+        <v>117.7</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>.txt×2</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>L1-49</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>L1 恒幅+DFOS</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>(组根)</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>6</v>
+      </c>
+      <c r="E118" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>.csv×5, .pdf×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>L1-50</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>L1 恒幅+DFOS</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>1</v>
+      </c>
+      <c r="E119" t="n">
+        <v>210.5</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>.pridb×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>L1-50</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>L1 恒幅+DFOS</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>LUNA</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>3</v>
+      </c>
+      <c r="E120" t="n">
+        <v>541.6</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>.txt×3</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>L1-50</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>L1 恒幅+DFOS</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>(组根)</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>6</v>
+      </c>
+      <c r="E121" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>.csv×5, .pdf×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>L1-51</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>L1 恒幅+DFOS</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>1</v>
+      </c>
+      <c r="E122" t="n">
+        <v>521.5</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>.pridb×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>L1-51</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>L1 恒幅+DFOS</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>LUNA</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>2</v>
+      </c>
+      <c r="E123" t="n">
+        <v>963.9</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>.txt×2</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>L1-51</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>L1 恒幅+DFOS</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>(组根)</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>6</v>
+      </c>
+      <c r="E124" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>.csv×5, .pdf×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>L1-52</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>L1 恒幅+DFOS</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>1</v>
+      </c>
+      <c r="E125" t="n">
+        <v>1426</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>.pridb×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>L1-52</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>L1 恒幅+DFOS</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>LUNA</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>1</v>
+      </c>
+      <c r="E126" t="n">
+        <v>4325.7</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>.txt×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>L1-52</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>L1 恒幅+DFOS</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>(组根)</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>6</v>
+      </c>
+      <c r="E127" t="n">
+        <v>33</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>.csv×5, .pdf×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>L1-54</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>L1 恒幅+DFOS</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>1</v>
+      </c>
+      <c r="E128" t="n">
+        <v>2196.1</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>.pridb×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>L1-54</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>L1 恒幅+DFOS</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>LUNA</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>1</v>
+      </c>
+      <c r="E129" t="n">
+        <v>5363.3</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>.txt×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>L1-54</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>L1 恒幅+DFOS</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>(组根)</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>6</v>
+      </c>
+      <c r="E130" t="n">
+        <v>47</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>.csv×5, .pdf×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>L1-55</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>L1 恒幅+DFOS</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>1</v>
+      </c>
+      <c r="E131" t="n">
+        <v>456.9</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>.pridb×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>L1-55</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>L1 恒幅+DFOS</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>LUNA</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>3</v>
+      </c>
+      <c r="E132" t="n">
+        <v>2214.9</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>.txt×3</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>L1-55</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>L1 恒幅+DFOS</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>(组根)</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>6</v>
+      </c>
+      <c r="E133" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>.csv×5, .pdf×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>L1-56</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>L1 恒幅+DFOS</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>1</v>
+      </c>
+      <c r="E134" t="n">
+        <v>2532</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>.pridb×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>L1-56</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>L1 恒幅+DFOS</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>LUNA</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>2</v>
+      </c>
+      <c r="E135" t="n">
+        <v>1883.8</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>.txt×2</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>L1-56</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>L1 恒幅+DFOS</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>(组根)</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>6</v>
+      </c>
+      <c r="E136" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>.csv×5, .pdf×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>L1-59</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>L1 恒幅+DFOS</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>2</v>
+      </c>
+      <c r="E137" t="n">
+        <v>510.1</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>.pridb×2</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>L1-59</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>L1 恒幅+DFOS</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>LUNA</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>3</v>
+      </c>
+      <c r="E138" t="n">
+        <v>1042.7</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>.txt×3</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>L1-59</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>L1 恒幅+DFOS</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>(组根)</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>6</v>
+      </c>
+      <c r="E139" t="n">
+        <v>10</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>.csv×5, .pdf×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
           <t>L1-60</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="B140" t="inlineStr">
         <is>
           <t>L1 恒幅+DFOS</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>1</v>
+      </c>
+      <c r="E140" t="n">
+        <v>963.9</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>.pridb×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>L1-60</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>L1 恒幅+DFOS</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>LUNA</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>2</v>
+      </c>
+      <c r="E141" t="n">
+        <v>1658.7</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>.txt×2</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>L1-60</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>L1 恒幅+DFOS</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
         <is>
           <t>(组根)</t>
         </is>
       </c>
-      <c r="D78" t="n">
+      <c r="D142" t="n">
         <v>6</v>
       </c>
-      <c r="E78" t="n">
+      <c r="E142" t="n">
         <v>15.3</v>
       </c>
-      <c r="F78" t="inlineStr">
+      <c r="F142" t="inlineStr">
         <is>
           <t>.csv×5, .pdf×1</t>
         </is>
@@ -9214,7 +11006,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9374,328 +11166,351 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>缺失模态</t>
+          <t>模态分布（2026-10-14 更正）</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>新组只有 AE + FBG，无 LUNA(DFOS)、无 PZT 数据</t>
+          <t>DFOS(LUNA) 只在 C1/C2；**PZT 导波在 C1 / C3 / C4 共 20 组**（C2 九组没有）；PZT 目录名两种：C3 为 `PZT/`，C1/C4 为 `PZT-&lt;N&gt;/`</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>老组那些依赖 DFOS 的证据（`e_strain`、DFOS 块级 HI、空间热图）在新组不可用</t>
+          <t>本表旧版把 PZT 列全填「无」，是因为判据写成单引号包着的 PZT 成员测试，只能命中不带编号的那种</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>新组按「AE 单源 + FBG 辅助」设计分析口径</t>
+          <t>依赖 DFOS 的口径对 C3/C4 不可用；依赖 PZT 的口径对 C2 不可用；PZT 可用口径与产物见 `README.md` §2.4 与 `docs/仓库地图.md` §3.4</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>载荷频率</t>
+          <t>「PZT」列的计数含义</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PDF 均未写频率（老组为 2 Hz）。现已从 AE+FBG 时序反解：变幅批 1.075 至 1.148 Hz；谱载批 1.821 至 2.119 Hz</t>
+          <t>`有(N)` 的 N = 磁盘上的 `State_*` 目录总数（不是 PZT 目录个数）。C1/C4 的状态分布在 `PZT-&lt;N&gt;/` 下（如 L1-03 的 `PZT-1` 只有 1 个状态、
+`PZT-2` 有 32 个），C3 全部在单个 `PZT/` 下</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>① 影响块定义与预警提前量口径；② 两组相差近一倍，不能合并处理</t>
+          <t>只数目录个数会被读成「只有 2 次采集」，实际是 33 个测量状态</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>向数据方书面确认（尤其变幅批的 1.1 Hz）；分组间差异是设备还是加载程序尚未知</t>
+          <t>进入跨机构口径前还会按 `MIN_STATES` 与数据完整性再过滤（L1-03 磁盘 33 个 → 口径内 30 个，见 `l1/results/pzt_crosslab_summary.csv`）</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AE 采集口径</t>
+          <t>载荷频率</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>新组为另一套采集系统（PCI2/DiSP），阈值与增益未知</t>
+          <t>PDF 均未写频率（老组为 2 Hz）。现已从 AE+FBG 时序反解：变幅批 1.075 至 1.148 Hz；谱载批 1.821 至 2.119 Hz</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>正是「AE 阈值/增益跨 campaign 不同」的又一例，跨分组比较须谨慎</t>
+          <t>① 影响块定义与预警提前量口径；② 两组相差近一倍，不能合并处理</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>先统计各组的 AE 事件数与幅值分布做横向体检</t>
+          <t>向数据方书面确认（尤其变幅批的 1.1 Hz）；分组间差异是设备还是加载程序尚未知</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AE 时钟平移</t>
+          <t>AE 采集口径</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>实测：谱载批(C4) 的 AE 文件时钟比 FBG 慢整 8 天；变幅批(C3) 两者同步</t>
+          <t>新组为另一套采集系统（PCI2/DiSP），阈值与增益未知</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>不做平移，AE 与 FBG 的时间轴差 8 天，跨模态时间对齐必然失败</t>
+          <t>正是「AE 阈值/增益跨 campaign 不同」的又一例，跨分组比较须谨慎</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>按批平移（C4 的 AE 时间 +8 天）；绝对日期待数据方确认</t>
+          <t>先统计各组的 AE 事件数与幅值分布做横向体检</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AE 分卷去重</t>
+          <t>AE 时钟平移</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>L1-27 有 1 个整卷 + 5 个分卷，6 个文件头部启动时刻完全相同（实测数据区字节数相等、仅 4 处共 40 字节不同 → 同一份数据）</t>
+          <t>实测：谱载批(C4) 的 AE 文件时钟比 FBG 慢整 8 天；变幅批(C3) 两者同步</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>直接叠加会把 1.18 GB 读成 2.37 GB，事件数翻倍</t>
+          <t>不做平移，AE 与 FBG 的时间轴差 8 天，跨模态时间对齐必然失败</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>按「同启动时刻 + 写入时间成簇」判定副本；用 probe_dta.py split/diff 验证</t>
+          <t>按批平移（C4 的 AE 时间 +8 天）；绝对日期待数据方确认</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AE 分卷续写</t>
+          <t>AE 分卷去重</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>L1-44-2/-3 也共用同一启动时刻，但写入时间相差 4 天（-2 达到 1.9 GB 后 -3 续写）</t>
+          <t>L1-27 有 1 个整卷 + 5 个分卷，6 个文件头部启动时刻完全相同（实测数据区字节数相等、仅 4 处共 40 字节不同 → 同一份数据）</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>这两种情形不能用同一规则判断，否则会把真正的数据当副本丢掉</t>
+          <t>直接叠加会把 1.18 GB 读成 2.37 GB，事件数翻倍</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>判据用「数据区是否逐字节可衔接」，不能只看文件名</t>
+          <t>按「同启动时刻 + 写入时间成簇」判定副本；用 probe_dta.py split/diff 验证</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>FBG 采集节奏</t>
+          <t>AE 分卷续写</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>突发式：每文件仅 20.0 s 数据（200 行 x 0.1 s）；文件间隔谱载部分组 420 s、变幅及 L1-30/35/36 为 240 s ⇒ 时间占空仅约 5%</t>
+          <t>L1-44-2/-3 也共用同一启动时刻，但写入时间相差 4 天（-2 达到 1.9 GB 后 -3 续写）</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>① 可当时间轴锚（用来校对 AE 钟差）；② 做不到「整段连续应变谱」；③ 有效观测时长仅 5.7 至 17.2 h，远小于日历跳度</t>
+          <t>这两种情形不能用同一规则判断，否则会把真正的数据当副本丢掉</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>时间轴/阶段划分靠 FBG；量化应变趋势只用这 20 s 窗口</t>
+          <t>判据用「数据区是否逐字节可衔接」，不能只看文件名</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>FBG 文件级覆盖率</t>
+          <t>FBG 采集节奏</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>活跃期（去榅 &gt; 2 h 空隙）文件覆盖率 98.6% 至 100.1%，基本完整；长空隙经 AE 交叉验证为试验暂停</t>
+          <t>突发式：每文件仅 20.0 s 数据（200 行 x 0.1 s）；文件间隔谱载部分组 420 s、变幅及 L1-30/35/36 为 240 s ⇒ 时间占空仅约 5%</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>曾因分母用错（拿整段日历时间当分母）误判为「覆盖率仅 39%」，已在文档中更正</t>
+          <t>① 可当时间轴锚（用来校对 AE 钟差）；② 做不到「整段连续应变谱」；③ 有效观测时长仅 5.7 至 17.2 h，远小于日历跳度</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>覆盖率分母只用小间隙段；长空隙归因看 AE 事件数</t>
+          <t>时间轴/阶段划分靠 FBG；量化应变趋势只用这 20 s 窗口</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>FBG 表头与数据行起点</t>
+          <t>FBG 文件级覆盖率</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>典型文件 260 行：0 至 36 设备表头 / 37 至 46 通道标定式（17 列，含数字但不是数据）/ 48 至 57 FBG 定义 / 59 列名行 / 60 至 259 数据</t>
+          <t>活跃期（去榅 &gt; 2 h 空隙）文件覆盖率 98.6% 至 100.1%，基本完整；长空隙经 AE 交叉验证为试验暂停</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>⚠️ 不能用「字段数 &gt;= 12」判数据行起点 —— 标定式有 17 列会被误收（曾据此误判解析器丢数据）</t>
+          <t>曾因分母用错（拿整段日历时间当分母）误判为「覆盖率仅 39%」，已在文档中更正</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>判据用「前两列能拼出时间戳 + 第 3 至 12 列可转浮点」</t>
+          <t>覆盖率分母只用小间隙段；长空隙归因看 AE 事件数</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>加载状态重建口径</t>
+          <t>FBG 表头与数据行起点</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>原来的「每帧 ±300 s 内凑到 &gt;= 3 个 FBG 窗才采信，否则赋全局均值」已改为 holdgap（零阶保持 + AE 静默守卫）</t>
+          <t>典型文件 260 行：0 至 36 设备表头 / 37 至 46 通道标定式（17 列，含数字但不是数据）/ 48 至 57 FBG 定义 / 59 列名行 / 60 至 259 数据</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>旧口径下 50% 至 70% 的帧拿到同一个常数，循环轴在那段退化成线性斜坡；L1-31 因此反解出 2.72 Hz（偏高 36%）</t>
+          <t>⚠️ 不能用「字段数 &gt;= 12」判数据行起点 —— 标定式有 17 列会被误收（曾据此误判解析器丢数据）</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>新口径下 L1-31 为 2.12 Hz（−5.6%），块内一致性大幅改善；旧口径用 ae_cycle.py --fill mean 复现</t>
+          <t>判据用「前两列能拼出时间戳 + 第 3 至 12 列可转浮点」</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>未提供的试件</t>
+          <t>加载状态重建口径</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>无 —— L1-22（变幅表）与 L1-23（一批表）已于 2026-10-09 由数据方补齐并接入</t>
+          <t>原来的「每帧 ±300 s 内凑到 &gt;= 3 个 FBG 窗才采信，否则赋全局均值」已改为 holdgap（零阶保持 + AE 静默守卫）</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>四个分组现在都是满员：C1 5 组 / C2 9 组 / C3 5 组 / C4 10 组 = 29 组</t>
+          <t>旧口径下 50% 至 70% 的帧拿到同一个常数，循环轴在那段退化成线性斜坡；L1-31 因此反解出 2.72 Hz（偏高 36%）</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>引用「29 组」而非旧文档的「27 组」；L1-22 带预置脱粘、L1-23 是两级载荷，见 details.md §45</t>
+          <t>新口径下 L1-31 为 2.12 Hz（−5.6%），块内一致性大幅改善；旧口径用 ae_cycle.py --fill mean 复现</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>传感器编号方向</t>
+          <t>未提供的试件</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>L1-24 的 AE 传感器标注为 L5R1…L1R5（与其余组的 L5R5…L1R1 相反）</t>
+          <t>无 —— L1-22（变幅表）与 L1-23（一批表）已于 2026-10-09 由数据方补齐并接入</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>若沿用「L#/R# 对应左右」的通道语义会左右错位</t>
+          <t>四个分组现在都是满员：C1 5 组 / C2 9 组 / C3 5 组 / C4 10 组 = 29 组</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>涉及 L1-24 的空间分析单独确认方向</t>
+          <t>引用「29 组」而非旧文档的「27 组」；L1-22 带预置脱粘、L1-23 是两级载荷，见 details.md §45</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>路径归属</t>
+          <t>传感器编号方向</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>29 组全在 E:\l1（数据本体只在外接盘，不入 D 盘仓库；2026-10-07 起不再用迁移脚本）</t>
+          <t>L1-24 的 AE 传感器标注为 L5R1…L1R5（与其余组的 L5R5…L1R1 相反）</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>仓库内相对路径 l1/L1-xx/ 对全部 29 组都有效（以前只有 13 组）</t>
+          <t>若沿用「L#/R# 对应左右」的通道语义会左右错位</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>换盘只改 paths.json 的 data_root 再跑 -Apply；数据侧新增的组在 paths.json 里补一条 item 即可被枚举到</t>
+          <t>涉及 L1-24 的空间分析单独确认方向</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>分析窗长</t>
+          <t>路径归属</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>剖面分析按 140 行切一个窗 ⇒ 变幅批（5 Hz）= 28.0 s；谱载批（10 Hz）= 14.0 s</t>
+          <t>29 组全在 E:\l1（数据本体只在外接盘，不入 D 盘仓库；2026-10-07 起不再用迁移脚本）</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>两组的「一块」物理时长不同，跨分组比 e_st 的采样密度会失真（形状漂移本身仍可比）</t>
+          <t>仓库内相对路径 l1/L1-xx/ 对全部 29 组都有效（以前只有 13 组）</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>跨分组只比趋势不比绝对值；窗长写在此处，避免后人误以为两组都是 28 s</t>
+          <t>换盘只改 paths.json 的 data_root 再跑 -Apply；数据侧新增的组在 paths.json 里补一条 item 即可被枚举到</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>分析窗长</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>剖面分析按 140 行切一个窗 ⇒ 变幅批（5 Hz）= 28.0 s；谱载批（10 Hz）= 14.0 s</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>两组的「一块」物理时长不同，跨分组比 e_st 的采样密度会失真（形状漂移本身仍可比）</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>跨分组只比趋势不比绝对值；窗长写在此处，避免后人误以为两组都是 28 s</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>load_h 的定义（勿误读）</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>load_h = sum(g) x 600 s / 3600，求和只跑在**AE 帧网格**上；而帧网格是稀疏的 —— 只为有事件的时段建帧（L1-25 有 1668 帧，帧号跨度却是 5586，最大缺口 576.33 h）</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>⇒ load_h 是「**AE 在录的时段内**的加载时长」，**不是日历占空比**；load_h / span_h 也不是日历占空比（span_h 跨过了中间的无帧空洞）</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>反解 f = n_f / load_h 是自洽的（分子分母共用同一张网格），可照用；但对外表述不得写成「加载占了多少日历时间」</t>
         </is>
